--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84b50a9ff1aa4084/Desktop/fanta-manageriale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="11_3D9D1AC753234BF4002E4BFD4A3740FA535EEFAA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7C11FA7-BA4F-BD4B-9D0C-9A9B9E59FBD4}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="11_3D9D1AC753234BF4002E4BFD4A3740FA535EEFAA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{208B606B-370A-2544-AF86-038B7A64D36F}"/>
   <bookViews>
     <workbookView xWindow="15140" yWindow="680" windowWidth="15100" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2151,10 +2151,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2739,24 +2735,24 @@
         <v>47</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J4" s="2">
         <f t="shared" si="1"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K4" t="s">
         <v>265</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="N4">
         <v>6</v>
@@ -2823,19 +2819,19 @@
         <v>14</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>5.75</v>
+        <v>5.86</v>
       </c>
       <c r="N5">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2896,13 +2892,13 @@
         <v>27</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="N6">
-        <v>7.71</v>
+        <v>7.5</v>
       </c>
       <c r="O6">
         <v>2</v>
@@ -3025,27 +3021,27 @@
         <v>36</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="2">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2">
         <f t="shared" si="1"/>
-        <v>24.5</v>
+        <v>26.25</v>
       </c>
       <c r="K8" t="s">
         <v>180</v>
       </c>
       <c r="L8">
+        <v>8</v>
+      </c>
+      <c r="M8">
+        <v>6.38</v>
+      </c>
+      <c r="N8">
         <v>7</v>
-      </c>
-      <c r="M8">
-        <v>6.43</v>
-      </c>
-      <c r="N8">
-        <v>7.14</v>
       </c>
       <c r="O8">
         <v>2</v>
@@ -3308,27 +3304,27 @@
         <v>56</v>
       </c>
       <c r="H12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="2">
         <f t="shared" si="0"/>
-        <v>4.8000000000000007</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="J12" s="2">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>40.25</v>
       </c>
       <c r="K12" t="s">
         <v>30</v>
       </c>
       <c r="L12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="N12">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -3395,13 +3391,13 @@
         <v>30</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="N13">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -4227,15 +4223,15 @@
         <v>45</v>
       </c>
       <c r="H25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I25" s="2">
         <f t="shared" si="0"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J25" s="2">
         <f t="shared" si="1"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="L25">
         <v>2</v>
@@ -4297,27 +4293,27 @@
         <v>60</v>
       </c>
       <c r="H26">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I26" s="2">
         <f t="shared" si="0"/>
-        <v>3.8000000000000003</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J26" s="2">
         <f t="shared" si="1"/>
-        <v>33.25</v>
+        <v>29.75</v>
       </c>
       <c r="K26" t="s">
         <v>265</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>6.07</v>
+        <v>5.94</v>
       </c>
       <c r="N26">
-        <v>6.79</v>
+        <v>6.5</v>
       </c>
       <c r="O26">
         <v>2</v>
@@ -4341,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="V26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -4370,30 +4366,30 @@
         <v>108</v>
       </c>
       <c r="H27">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I27" s="2">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J27" s="2">
         <f t="shared" si="1"/>
-        <v>22.75</v>
+        <v>26.25</v>
       </c>
       <c r="K27" t="s">
         <v>27</v>
       </c>
       <c r="L27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>6.07</v>
+        <v>6.19</v>
       </c>
       <c r="N27">
-        <v>6.71</v>
+        <v>7.25</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -4411,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V27">
         <v>1</v>
@@ -4513,27 +4509,27 @@
         <v>39</v>
       </c>
       <c r="H29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I29" s="2">
         <f t="shared" si="0"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J29" s="2">
         <f t="shared" si="1"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K29" t="s">
         <v>180</v>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="N29">
-        <v>5.92</v>
+        <v>5.86</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4729,33 +4725,33 @@
         <v>26</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="2">
         <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J32" s="2">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="K32" t="s">
         <v>30</v>
       </c>
       <c r="L32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="N32">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4802,30 +4798,30 @@
         <v>41</v>
       </c>
       <c r="H33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I33" s="2">
         <f t="shared" si="0"/>
-        <v>3.8000000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="J33" s="2">
         <f t="shared" si="1"/>
-        <v>33.25</v>
+        <v>36.75</v>
       </c>
       <c r="K33" t="s">
         <v>127</v>
       </c>
       <c r="L33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>6.31</v>
+        <v>6.44</v>
       </c>
       <c r="N33">
-        <v>6.88</v>
+        <v>7.17</v>
       </c>
       <c r="O33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -4834,16 +4830,16 @@
         <v>0</v>
       </c>
       <c r="R33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S33">
         <v>1</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -4889,13 +4885,13 @@
         <v>95</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>6.25</v>
+        <v>6.21</v>
       </c>
       <c r="N34">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -5088,15 +5084,15 @@
         <v>108</v>
       </c>
       <c r="H37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I37" s="2">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J37" s="2">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -5158,15 +5154,15 @@
         <v>47</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38" s="2">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="J38" s="2">
         <f t="shared" si="1"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="L38">
         <v>2</v>
@@ -5228,15 +5224,15 @@
         <v>47</v>
       </c>
       <c r="H39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" s="2">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J39" s="2">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K39" t="s">
         <v>27</v>
@@ -5371,15 +5367,15 @@
         <v>42</v>
       </c>
       <c r="H41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I41" s="2">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J41" s="2">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K41" t="s">
         <v>95</v>
@@ -5444,27 +5440,27 @@
         <v>62</v>
       </c>
       <c r="H42">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I42" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J42" s="2">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="K42" t="s">
         <v>127</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M42">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="N42">
-        <v>6.93</v>
+        <v>6.75</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -5488,7 +5484,7 @@
         <v>2</v>
       </c>
       <c r="V42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42">
         <v>0</v>
@@ -5528,13 +5524,13 @@
         <v>7</v>
       </c>
       <c r="L43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M43">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="N43">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5884,13 +5880,13 @@
         <v>265</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="N48">
-        <v>6.88</v>
+        <v>6.7</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -5957,13 +5953,13 @@
         <v>30</v>
       </c>
       <c r="L49">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M49">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>6.94</v>
       </c>
       <c r="O49">
         <v>2</v>
@@ -6030,7 +6026,7 @@
         <v>27</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M50">
         <v>5.5</v>
@@ -6089,15 +6085,15 @@
         <v>33</v>
       </c>
       <c r="H51">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I51" s="2">
         <f t="shared" si="0"/>
-        <v>3.8000000000000003</v>
+        <v>3.6</v>
       </c>
       <c r="J51" s="2">
         <f t="shared" si="1"/>
-        <v>33.25</v>
+        <v>31.5</v>
       </c>
       <c r="K51" t="s">
         <v>127</v>
@@ -6232,27 +6228,27 @@
         <v>34</v>
       </c>
       <c r="H53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I53" s="2">
         <f t="shared" si="0"/>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J53" s="2">
         <f t="shared" si="1"/>
-        <v>19.25</v>
+        <v>17.5</v>
       </c>
       <c r="K53" t="s">
         <v>95</v>
       </c>
       <c r="L53">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M53">
         <v>6</v>
       </c>
       <c r="N53">
-        <v>5.93</v>
+        <v>5.88</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -6276,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="V53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -6375,33 +6371,33 @@
         <v>26</v>
       </c>
       <c r="H55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I55" s="2">
         <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="K55" t="s">
         <v>265</v>
       </c>
       <c r="L55">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="N55">
-        <v>4.1900000000000004</v>
+        <v>3.94</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -6448,15 +6444,15 @@
         <v>33</v>
       </c>
       <c r="H56">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I56" s="2">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J56" s="2">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>26.25</v>
       </c>
       <c r="K56" t="s">
         <v>27</v>
@@ -6521,15 +6517,15 @@
         <v>33</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I57" s="2">
         <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J57" s="2">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="L57">
         <v>4</v>
@@ -6591,15 +6587,15 @@
         <v>41</v>
       </c>
       <c r="H58">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I58" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J58" s="2">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="K58" t="s">
         <v>127</v>
@@ -6664,15 +6660,15 @@
         <v>152</v>
       </c>
       <c r="H59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I59" s="2">
         <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J59" s="2">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="L59">
         <v>2</v>
@@ -6734,24 +6730,24 @@
         <v>26</v>
       </c>
       <c r="H60">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I60" s="2">
         <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J60" s="2">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="K60" t="s">
         <v>95</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M60">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="N60">
         <v>6</v>
@@ -6760,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -6807,15 +6803,15 @@
         <v>183</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J61" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="K61" t="s">
         <v>180</v>
@@ -6894,13 +6890,13 @@
         <v>180</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M62">
         <v>6.5</v>
       </c>
       <c r="N62">
-        <v>7.92</v>
+        <v>7.71</v>
       </c>
       <c r="O62">
         <v>3</v>
@@ -6953,18 +6949,18 @@
         <v>39</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63" s="2">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J63" s="2">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63">
         <v>6</v>
@@ -7023,27 +7019,27 @@
         <v>34</v>
       </c>
       <c r="H64">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I64" s="2">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J64" s="2">
         <f t="shared" si="1"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K64" t="s">
         <v>180</v>
       </c>
       <c r="L64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M64">
-        <v>6.14</v>
+        <v>6.06</v>
       </c>
       <c r="N64">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -7166,15 +7162,15 @@
         <v>45</v>
       </c>
       <c r="H66">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I66" s="2">
         <f t="shared" ref="I66:I129" si="2">H66*0.2</f>
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J66" s="2">
         <f t="shared" ref="J66:J129" si="3">H66*1.75</f>
-        <v>47.25</v>
+        <v>45.5</v>
       </c>
       <c r="K66" t="s">
         <v>234</v>
@@ -7309,15 +7305,15 @@
         <v>34</v>
       </c>
       <c r="H68">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I68" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J68" s="2">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="L68">
         <v>2</v>
@@ -7379,27 +7375,27 @@
         <v>100</v>
       </c>
       <c r="H69">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I69" s="2">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="J69" s="2">
         <f t="shared" si="3"/>
-        <v>43.75</v>
+        <v>42</v>
       </c>
       <c r="K69" t="s">
         <v>95</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>6.6</v>
+        <v>6.33</v>
       </c>
       <c r="N69">
-        <v>7.9</v>
+        <v>7.42</v>
       </c>
       <c r="O69">
         <v>2</v>
@@ -7525,30 +7521,30 @@
         <v>91</v>
       </c>
       <c r="H71">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I71" s="2">
         <f t="shared" si="2"/>
-        <v>3.8000000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="J71" s="2">
         <f t="shared" si="3"/>
-        <v>33.25</v>
+        <v>36.75</v>
       </c>
       <c r="K71" t="s">
         <v>180</v>
       </c>
       <c r="L71">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M71">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="N71">
-        <v>7.25</v>
+        <v>7.56</v>
       </c>
       <c r="O71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P71">
         <v>0</v>
@@ -7612,19 +7608,19 @@
         <v>180</v>
       </c>
       <c r="L72">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M72">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="N72">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -7682,13 +7678,13 @@
         <v>8.75</v>
       </c>
       <c r="L73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="N73">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -8021,27 +8017,27 @@
         <v>47</v>
       </c>
       <c r="H78">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I78" s="2">
         <f t="shared" si="2"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J78" s="2">
         <f t="shared" si="3"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K78" t="s">
         <v>95</v>
       </c>
       <c r="L78">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M78">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="N78">
-        <v>6.44</v>
+        <v>6.33</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -8167,15 +8163,15 @@
         <v>34</v>
       </c>
       <c r="H80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I80" s="2">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J80" s="2">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="K80" t="s">
         <v>30</v>
@@ -8310,15 +8306,15 @@
         <v>47</v>
       </c>
       <c r="H82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I82" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J82" s="2">
         <f t="shared" si="3"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -8453,24 +8449,24 @@
         <v>91</v>
       </c>
       <c r="H84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I84" s="2">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J84" s="2">
         <f t="shared" si="3"/>
+        <v>8.75</v>
+      </c>
+      <c r="L84">
         <v>7</v>
       </c>
-      <c r="L84">
-        <v>6</v>
-      </c>
       <c r="M84">
-        <v>5.58</v>
+        <v>5.71</v>
       </c>
       <c r="N84">
-        <v>5.5</v>
+        <v>5.79</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -8491,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V84">
         <v>1</v>
@@ -8523,27 +8519,27 @@
         <v>100</v>
       </c>
       <c r="H85">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I85" s="2">
         <f t="shared" si="2"/>
-        <v>2.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J85" s="2">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="K85" t="s">
         <v>95</v>
       </c>
       <c r="L85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M85">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="N85">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -8567,7 +8563,7 @@
         <v>0</v>
       </c>
       <c r="V85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85">
         <v>0</v>
@@ -8596,27 +8592,27 @@
         <v>34</v>
       </c>
       <c r="H86">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I86" s="2">
         <f t="shared" si="2"/>
-        <v>3.8000000000000003</v>
+        <v>3.6</v>
       </c>
       <c r="J86" s="2">
         <f t="shared" si="3"/>
-        <v>33.25</v>
+        <v>31.5</v>
       </c>
       <c r="K86" t="s">
         <v>30</v>
       </c>
       <c r="L86">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M86">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="N86">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="O86">
         <v>2</v>
@@ -8739,27 +8735,27 @@
         <v>26</v>
       </c>
       <c r="H88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I88" s="2">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J88" s="2">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="K88" t="s">
         <v>234</v>
       </c>
       <c r="L88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="N88">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -8885,27 +8881,27 @@
         <v>39</v>
       </c>
       <c r="H90">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I90" s="2">
         <f t="shared" si="2"/>
-        <v>2.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J90" s="2">
         <f t="shared" si="3"/>
-        <v>19.25</v>
+        <v>21</v>
       </c>
       <c r="K90" t="s">
         <v>265</v>
       </c>
       <c r="L90">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M90">
         <v>6.06</v>
       </c>
       <c r="N90">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -8926,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="U90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V90">
         <v>1</v>
@@ -8969,13 +8965,13 @@
         <v>8.75</v>
       </c>
       <c r="L91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M91">
-        <v>5.88</v>
+        <v>5.8</v>
       </c>
       <c r="N91">
-        <v>5.88</v>
+        <v>5.8</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -9098,27 +9094,27 @@
         <v>45</v>
       </c>
       <c r="H93">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I93" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J93" s="2">
         <f t="shared" si="3"/>
-        <v>26.25</v>
+        <v>24.5</v>
       </c>
       <c r="K93" t="s">
         <v>265</v>
       </c>
       <c r="L93">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M93">
-        <v>6.44</v>
+        <v>6.39</v>
       </c>
       <c r="N93">
-        <v>7.56</v>
+        <v>7.06</v>
       </c>
       <c r="O93">
         <v>3</v>
@@ -9130,13 +9126,13 @@
         <v>0</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93">
         <v>0</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U93">
         <v>0</v>
@@ -9381,24 +9377,24 @@
         <v>34</v>
       </c>
       <c r="H97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I97" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J97" s="2">
         <f t="shared" si="3"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M97">
-        <v>5.25</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="N97">
-        <v>5.25</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -9465,13 +9461,13 @@
         <v>156</v>
       </c>
       <c r="L98">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M98">
-        <v>5.93</v>
+        <v>5.94</v>
       </c>
       <c r="N98">
-        <v>5.93</v>
+        <v>5.94</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -9524,15 +9520,15 @@
         <v>78</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I99" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J99" s="2">
         <f t="shared" si="3"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L99">
         <v>3</v>
@@ -9594,15 +9590,15 @@
         <v>41</v>
       </c>
       <c r="H100">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I100" s="2">
         <f t="shared" si="2"/>
-        <v>2.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J100" s="2">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="L100">
         <v>6</v>
@@ -9664,15 +9660,15 @@
         <v>45</v>
       </c>
       <c r="H101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I101" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J101" s="2">
         <f t="shared" si="3"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L101">
         <v>7</v>
@@ -9734,24 +9730,24 @@
         <v>34</v>
       </c>
       <c r="H102">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I102" s="2">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J102" s="2">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="L102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M102">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="N102">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -9818,13 +9814,13 @@
         <v>265</v>
       </c>
       <c r="L103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M103">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="N103">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="O103">
         <v>1</v>
@@ -10017,24 +10013,24 @@
         <v>34</v>
       </c>
       <c r="H106">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I106" s="2">
         <f t="shared" si="2"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="J106" s="2">
         <f t="shared" si="3"/>
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="L106">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M106">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="N106">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -10160,33 +10156,33 @@
         <v>26</v>
       </c>
       <c r="H108">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I108" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J108" s="2">
         <f t="shared" si="3"/>
-        <v>26.25</v>
+        <v>22.75</v>
       </c>
       <c r="K108" t="s">
         <v>27</v>
       </c>
       <c r="L108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M108">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="N108">
-        <v>5.31</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="O108">
         <v>0</v>
       </c>
       <c r="P108">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -10247,13 +10243,13 @@
         <v>127</v>
       </c>
       <c r="L109">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M109">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="N109">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -10306,15 +10302,15 @@
         <v>47</v>
       </c>
       <c r="H110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I110" s="2">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J110" s="2">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -10449,30 +10445,30 @@
         <v>26</v>
       </c>
       <c r="H112">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I112" s="2">
         <f t="shared" si="2"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J112" s="2">
         <f t="shared" si="3"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="L112">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M112">
-        <v>6.38</v>
+        <v>6.39</v>
       </c>
       <c r="N112">
-        <v>5.25</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="O112">
         <v>0</v>
       </c>
       <c r="P112">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -10533,13 +10529,13 @@
         <v>265</v>
       </c>
       <c r="L113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M113">
-        <v>5.83</v>
+        <v>5.93</v>
       </c>
       <c r="N113">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O113">
         <v>1</v>
@@ -10735,24 +10731,24 @@
         <v>42</v>
       </c>
       <c r="H116">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I116" s="2">
         <f t="shared" si="2"/>
-        <v>1.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J116" s="2">
         <f t="shared" si="3"/>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="L116">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M116">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="N116">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="O116">
         <v>1</v>
@@ -11035,13 +11031,13 @@
         <v>127</v>
       </c>
       <c r="L120">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M120">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="N120">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -11094,33 +11090,33 @@
         <v>26</v>
       </c>
       <c r="H121">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I121" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J121" s="2">
         <f t="shared" si="3"/>
-        <v>26.25</v>
+        <v>22.75</v>
       </c>
       <c r="K121" t="s">
         <v>127</v>
       </c>
       <c r="L121">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M121">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="N121">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="O121">
         <v>0</v>
       </c>
       <c r="P121">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q121">
         <v>1</v>
@@ -11167,24 +11163,24 @@
         <v>39</v>
       </c>
       <c r="H122">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I122" s="2">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J122" s="2">
         <f t="shared" si="3"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="L122">
+        <v>7</v>
+      </c>
+      <c r="M122">
         <v>6</v>
       </c>
-      <c r="M122">
-        <v>5.92</v>
-      </c>
       <c r="N122">
-        <v>5.92</v>
+        <v>6.14</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -11205,7 +11201,7 @@
         <v>0</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122">
         <v>0</v>
@@ -11237,24 +11233,24 @@
         <v>41</v>
       </c>
       <c r="H123">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I123" s="2">
         <f t="shared" si="2"/>
-        <v>2.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J123" s="2">
         <f t="shared" si="3"/>
-        <v>19.25</v>
+        <v>21</v>
       </c>
       <c r="L123">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M123">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="N123">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -11447,27 +11443,27 @@
         <v>60</v>
       </c>
       <c r="H126">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I126" s="2">
         <f t="shared" si="2"/>
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J126" s="2">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>31.5</v>
       </c>
       <c r="L126">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M126">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="N126">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -11517,27 +11513,27 @@
         <v>47</v>
       </c>
       <c r="H127">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I127" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J127" s="2">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="K127" t="s">
         <v>234</v>
       </c>
       <c r="L127">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M127">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="N127">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -11671,13 +11667,13 @@
         <v>14</v>
       </c>
       <c r="L129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M129">
-        <v>5.88</v>
+        <v>5.8</v>
       </c>
       <c r="N129">
-        <v>6.62</v>
+        <v>6.3</v>
       </c>
       <c r="O129">
         <v>1</v>
@@ -11701,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129">
         <v>1</v>
@@ -11800,24 +11796,24 @@
         <v>42</v>
       </c>
       <c r="H131">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I131" s="2">
         <f t="shared" si="4"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J131" s="2">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="L131">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M131">
-        <v>5.93</v>
+        <v>5.81</v>
       </c>
       <c r="N131">
-        <v>6.07</v>
+        <v>5.94</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -12083,15 +12079,15 @@
         <v>34</v>
       </c>
       <c r="H135">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I135" s="2">
         <f t="shared" si="4"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J135" s="2">
         <f t="shared" si="5"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="L135">
         <v>4</v>
@@ -12363,27 +12359,27 @@
         <v>42</v>
       </c>
       <c r="H139">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I139" s="2">
         <f t="shared" si="4"/>
-        <v>2.8000000000000003</v>
+        <v>3</v>
       </c>
       <c r="J139" s="2">
         <f t="shared" si="5"/>
-        <v>24.5</v>
+        <v>26.25</v>
       </c>
       <c r="K139" t="s">
         <v>156</v>
       </c>
       <c r="L139">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M139">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="N139">
-        <v>6.64</v>
+        <v>6.81</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -12404,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="U139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V139">
         <v>1</v>
@@ -12436,24 +12432,24 @@
         <v>34</v>
       </c>
       <c r="H140">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I140" s="2">
         <f t="shared" si="4"/>
-        <v>1.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J140" s="2">
         <f t="shared" si="5"/>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="L140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M140">
         <v>6.5</v>
       </c>
       <c r="N140">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -12474,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V140">
         <v>0</v>
@@ -12576,27 +12572,27 @@
         <v>45</v>
       </c>
       <c r="H142">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I142" s="2">
         <f t="shared" si="4"/>
-        <v>4.8000000000000007</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="J142" s="2">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>40.25</v>
       </c>
       <c r="K142" t="s">
         <v>156</v>
       </c>
       <c r="L142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M142">
-        <v>6.1</v>
+        <v>6.17</v>
       </c>
       <c r="N142">
-        <v>7.3</v>
+        <v>7.17</v>
       </c>
       <c r="O142">
         <v>2</v>
@@ -12649,15 +12645,15 @@
         <v>34</v>
       </c>
       <c r="H143">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I143" s="2">
         <f t="shared" si="4"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J143" s="2">
         <f t="shared" si="5"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K143" t="s">
         <v>27</v>
@@ -12733,13 +12729,13 @@
         <v>14</v>
       </c>
       <c r="L144">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M144">
-        <v>6.12</v>
+        <v>6.1</v>
       </c>
       <c r="N144">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -12935,33 +12931,33 @@
         <v>26</v>
       </c>
       <c r="H147">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I147" s="2">
         <f t="shared" si="4"/>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J147" s="2">
         <f t="shared" si="5"/>
-        <v>1.75</v>
+        <v>7</v>
       </c>
       <c r="L147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M147">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="N147">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="O147">
         <v>0</v>
       </c>
       <c r="P147">
+        <v>8</v>
+      </c>
+      <c r="Q147">
         <v>2</v>
-      </c>
-      <c r="Q147">
-        <v>0</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -13016,13 +13012,13 @@
         <v>17.5</v>
       </c>
       <c r="L148">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M148">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="N148">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -13089,13 +13085,13 @@
         <v>95</v>
       </c>
       <c r="L149">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M149">
-        <v>6.86</v>
+        <v>6.81</v>
       </c>
       <c r="N149">
-        <v>9.2100000000000009</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="O149">
         <v>5</v>
@@ -13291,30 +13287,30 @@
         <v>100</v>
       </c>
       <c r="H152">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I152" s="2">
         <f t="shared" si="4"/>
-        <v>2.8000000000000003</v>
+        <v>3.2</v>
       </c>
       <c r="J152" s="2">
         <f t="shared" si="5"/>
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="K152" t="s">
         <v>265</v>
       </c>
       <c r="L152">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M152">
-        <v>6.19</v>
+        <v>6.28</v>
       </c>
       <c r="N152">
-        <v>7.69</v>
+        <v>7.94</v>
       </c>
       <c r="O152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P152">
         <v>0</v>
@@ -13378,13 +13374,13 @@
         <v>95</v>
       </c>
       <c r="L153">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M153">
-        <v>5.81</v>
+        <v>5.72</v>
       </c>
       <c r="N153">
-        <v>6.25</v>
+        <v>6.11</v>
       </c>
       <c r="O153">
         <v>1</v>
@@ -13437,15 +13433,15 @@
         <v>33</v>
       </c>
       <c r="H154">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I154" s="2">
         <f t="shared" si="4"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J154" s="2">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K154" t="s">
         <v>156</v>
@@ -13521,13 +13517,13 @@
         <v>8.75</v>
       </c>
       <c r="L155">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M155">
-        <v>5.75</v>
+        <v>5.72</v>
       </c>
       <c r="N155">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -13661,13 +13657,13 @@
         <v>7</v>
       </c>
       <c r="L157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M157">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="N157">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="O157">
         <v>0</v>
@@ -13720,24 +13716,24 @@
         <v>34</v>
       </c>
       <c r="H158">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I158" s="2">
         <f t="shared" si="4"/>
-        <v>1.2000000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J158" s="2">
         <f t="shared" si="5"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="L158">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M158">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="N158">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="O158">
         <v>0</v>
@@ -13860,30 +13856,30 @@
         <v>26</v>
       </c>
       <c r="H160">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I160" s="2">
         <f t="shared" si="4"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J160" s="2">
         <f t="shared" si="5"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="L160">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M160">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="N160">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="O160">
         <v>0</v>
       </c>
       <c r="P160">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -13930,24 +13926,24 @@
         <v>36</v>
       </c>
       <c r="H161">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I161" s="2">
         <f t="shared" si="4"/>
-        <v>2.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J161" s="2">
         <f t="shared" si="5"/>
-        <v>19.25</v>
+        <v>21</v>
       </c>
       <c r="L161">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M161">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="N161">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="O161">
         <v>1</v>
@@ -14000,27 +13996,27 @@
         <v>45</v>
       </c>
       <c r="H162">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I162" s="2">
         <f t="shared" si="4"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J162" s="2">
         <f t="shared" si="5"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K162" t="s">
         <v>30</v>
       </c>
       <c r="L162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M162">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="N162">
-        <v>6.6</v>
+        <v>6.42</v>
       </c>
       <c r="O162">
         <v>1</v>
@@ -14073,27 +14069,27 @@
         <v>78</v>
       </c>
       <c r="H163">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I163" s="2">
         <f t="shared" si="4"/>
-        <v>2.4000000000000004</v>
+        <v>2</v>
       </c>
       <c r="J163" s="2">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="K163" t="s">
         <v>27</v>
       </c>
       <c r="L163">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M163">
-        <v>6.06</v>
+        <v>5.89</v>
       </c>
       <c r="N163">
-        <v>6.06</v>
+        <v>5.89</v>
       </c>
       <c r="O163">
         <v>0</v>
@@ -14160,13 +14156,13 @@
         <v>30</v>
       </c>
       <c r="L164">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M164">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="N164">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="O164">
         <v>0</v>
@@ -14233,13 +14229,13 @@
         <v>127</v>
       </c>
       <c r="L165">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M165">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="N165">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -14260,7 +14256,7 @@
         <v>0</v>
       </c>
       <c r="U165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V165">
         <v>0</v>
@@ -14373,13 +14369,13 @@
         <v>12.25</v>
       </c>
       <c r="L167">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M167">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="N167">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -14432,27 +14428,27 @@
         <v>34</v>
       </c>
       <c r="H168">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I168" s="2">
         <f t="shared" si="4"/>
-        <v>2.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J168" s="2">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="K168" t="s">
         <v>27</v>
       </c>
       <c r="L168">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M168">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="N168">
-        <v>6.06</v>
+        <v>6</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -14505,15 +14501,15 @@
         <v>33</v>
       </c>
       <c r="H169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I169" s="2">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J169" s="2">
         <f t="shared" si="5"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L169">
         <v>5</v>
@@ -14575,27 +14571,27 @@
         <v>45</v>
       </c>
       <c r="H170">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I170" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J170" s="2">
         <f t="shared" si="5"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="K170" t="s">
         <v>127</v>
       </c>
       <c r="L170">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M170">
-        <v>6.25</v>
+        <v>6.21</v>
       </c>
       <c r="N170">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -14648,15 +14644,15 @@
         <v>26</v>
       </c>
       <c r="H171">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I171" s="2">
         <f t="shared" si="4"/>
-        <v>2.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J171" s="2">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="K171" t="s">
         <v>234</v>
@@ -14721,15 +14717,15 @@
         <v>45</v>
       </c>
       <c r="H172">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I172" s="2">
         <f t="shared" si="4"/>
-        <v>2.6</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J172" s="2">
         <f t="shared" si="5"/>
-        <v>22.75</v>
+        <v>21</v>
       </c>
       <c r="K172" t="s">
         <v>95</v>
@@ -14794,24 +14790,24 @@
         <v>47</v>
       </c>
       <c r="H173">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I173" s="2">
         <f t="shared" si="4"/>
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J173" s="2">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="L173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M173">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="N173">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="O173">
         <v>1</v>
@@ -14864,15 +14860,15 @@
         <v>62</v>
       </c>
       <c r="H174">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I174" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J174" s="2">
         <f t="shared" si="5"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="L174">
         <v>4</v>
@@ -14948,13 +14944,13 @@
         <v>265</v>
       </c>
       <c r="L175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M175">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="N175">
-        <v>5.58</v>
+        <v>5.57</v>
       </c>
       <c r="O175">
         <v>0</v>
@@ -15018,13 +15014,13 @@
         <v>12.25</v>
       </c>
       <c r="L176">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M176">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="N176">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="O176">
         <v>0</v>
@@ -15077,24 +15073,24 @@
         <v>47</v>
       </c>
       <c r="H177">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I177" s="2">
         <f t="shared" si="4"/>
-        <v>2.4000000000000004</v>
+        <v>2.6</v>
       </c>
       <c r="J177" s="2">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="L177">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M177">
-        <v>6.29</v>
+        <v>6.31</v>
       </c>
       <c r="N177">
-        <v>6.64</v>
+        <v>6.56</v>
       </c>
       <c r="O177">
         <v>1</v>
@@ -15118,7 +15114,7 @@
         <v>0</v>
       </c>
       <c r="V177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W177">
         <v>0</v>
@@ -15301,13 +15297,13 @@
         <v>8.75</v>
       </c>
       <c r="L180">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M180">
-        <v>5.71</v>
+        <v>5.69</v>
       </c>
       <c r="N180">
-        <v>5.71</v>
+        <v>5.69</v>
       </c>
       <c r="O180">
         <v>0</v>
@@ -15430,27 +15426,27 @@
         <v>33</v>
       </c>
       <c r="H182">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I182" s="2">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J182" s="2">
         <f t="shared" si="5"/>
+        <v>10.5</v>
+      </c>
+      <c r="L182">
+        <v>3</v>
+      </c>
+      <c r="M182">
+        <v>6</v>
+      </c>
+      <c r="N182">
         <v>7</v>
       </c>
-      <c r="L182">
-        <v>2</v>
-      </c>
-      <c r="M182">
-        <v>5.5</v>
-      </c>
-      <c r="N182">
-        <v>5.5</v>
-      </c>
       <c r="O182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P182">
         <v>0</v>
@@ -15459,10 +15455,10 @@
         <v>0</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T182">
         <v>0</v>
@@ -15500,27 +15496,27 @@
         <v>34</v>
       </c>
       <c r="H183">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I183" s="2">
         <f t="shared" si="4"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J183" s="2">
         <f t="shared" si="5"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K183" t="s">
         <v>30</v>
       </c>
       <c r="L183">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M183">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="N183">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="O183">
         <v>0</v>
@@ -15573,24 +15569,24 @@
         <v>34</v>
       </c>
       <c r="H184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I184" s="2">
         <f t="shared" si="4"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J184" s="2">
         <f t="shared" si="5"/>
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="L184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M184">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O184">
         <v>0</v>
@@ -15643,30 +15639,30 @@
         <v>108</v>
       </c>
       <c r="H185">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I185" s="2">
         <f t="shared" si="4"/>
-        <v>1.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J185" s="2">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>19.25</v>
       </c>
       <c r="K185" t="s">
         <v>95</v>
       </c>
       <c r="L185">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M185">
-        <v>6.1</v>
+        <v>6.33</v>
       </c>
       <c r="N185">
-        <v>6.5</v>
+        <v>7.33</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P185">
         <v>0</v>
@@ -15684,7 +15680,7 @@
         <v>0</v>
       </c>
       <c r="U185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V185">
         <v>0</v>
@@ -15856,27 +15852,27 @@
         <v>33</v>
       </c>
       <c r="H188">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I188" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J188" s="2">
         <f t="shared" si="5"/>
-        <v>26.25</v>
+        <v>29.75</v>
       </c>
       <c r="L188">
+        <v>9</v>
+      </c>
+      <c r="M188">
+        <v>6.61</v>
+      </c>
+      <c r="N188">
+        <v>9.11</v>
+      </c>
+      <c r="O188">
         <v>8</v>
-      </c>
-      <c r="M188">
-        <v>6.56</v>
-      </c>
-      <c r="N188">
-        <v>9</v>
-      </c>
-      <c r="O188">
-        <v>7</v>
       </c>
       <c r="P188">
         <v>0</v>
@@ -16077,13 +16073,13 @@
         <v>8.75</v>
       </c>
       <c r="L191">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M191">
-        <v>5.81</v>
+        <v>5.78</v>
       </c>
       <c r="N191">
-        <v>5.75</v>
+        <v>5.72</v>
       </c>
       <c r="O191">
         <v>0</v>
@@ -16206,21 +16202,21 @@
         <v>183</v>
       </c>
       <c r="H193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I193" s="2">
         <f t="shared" si="4"/>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J193" s="2">
         <f t="shared" si="5"/>
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="K193" t="s">
         <v>180</v>
       </c>
       <c r="L193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M193">
         <v>6</v>
@@ -16360,13 +16356,13 @@
         <v>12.25</v>
       </c>
       <c r="L195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M195">
-        <v>6.33</v>
+        <v>6.12</v>
       </c>
       <c r="N195">
-        <v>7.33</v>
+        <v>6.88</v>
       </c>
       <c r="O195">
         <v>1</v>
@@ -16419,24 +16415,24 @@
         <v>41</v>
       </c>
       <c r="H196">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I196" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J196" s="2">
         <f t="shared" si="7"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="L196">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M196">
-        <v>6.2</v>
+        <v>6.17</v>
       </c>
       <c r="N196">
-        <v>6.7</v>
+        <v>6.58</v>
       </c>
       <c r="O196">
         <v>1</v>
@@ -16559,27 +16555,27 @@
         <v>47</v>
       </c>
       <c r="H198">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I198" s="2">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J198" s="2">
         <f t="shared" si="7"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K198" t="s">
         <v>265</v>
       </c>
       <c r="L198">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M198">
-        <v>6.12</v>
+        <v>5.9</v>
       </c>
       <c r="N198">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="O198">
         <v>0</v>
@@ -16646,13 +16642,13 @@
         <v>265</v>
       </c>
       <c r="L199">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M199">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="N199">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="O199">
         <v>1</v>
@@ -16705,27 +16701,27 @@
         <v>183</v>
       </c>
       <c r="H200">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I200" s="2">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J200" s="2">
         <f t="shared" si="7"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K200" t="s">
         <v>234</v>
       </c>
       <c r="L200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M200">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="N200">
-        <v>5.62</v>
+        <v>5.3</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -16778,27 +16774,27 @@
         <v>34</v>
       </c>
       <c r="H201">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I201" s="2">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J201" s="2">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K201" t="s">
         <v>127</v>
       </c>
       <c r="L201">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M201">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="N201">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="O201">
         <v>0</v>
@@ -16851,15 +16847,15 @@
         <v>39</v>
       </c>
       <c r="H202">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I202" s="2">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J202" s="2">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="L202">
         <v>2</v>
@@ -16991,24 +16987,24 @@
         <v>42</v>
       </c>
       <c r="H204">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I204" s="2">
         <f t="shared" si="6"/>
-        <v>2.4000000000000004</v>
+        <v>2.6</v>
       </c>
       <c r="J204" s="2">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="L204">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M204">
-        <v>6.06</v>
+        <v>6</v>
       </c>
       <c r="N204">
-        <v>6.75</v>
+        <v>6.61</v>
       </c>
       <c r="O204">
         <v>2</v>
@@ -17061,27 +17057,27 @@
         <v>45</v>
       </c>
       <c r="H205">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I205" s="2">
         <f t="shared" si="6"/>
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J205" s="2">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>26.25</v>
       </c>
       <c r="K205" t="s">
         <v>156</v>
       </c>
       <c r="L205">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M205">
-        <v>6.19</v>
+        <v>6.22</v>
       </c>
       <c r="N205">
-        <v>6.19</v>
+        <v>6.22</v>
       </c>
       <c r="O205">
         <v>0</v>
@@ -17134,15 +17130,15 @@
         <v>62</v>
       </c>
       <c r="H206">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I206" s="2">
         <f t="shared" si="6"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J206" s="2">
         <f t="shared" si="7"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="K206" t="s">
         <v>234</v>
@@ -17207,15 +17203,15 @@
         <v>78</v>
       </c>
       <c r="H207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I207" s="2">
         <f t="shared" si="6"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="J207" s="2">
         <f t="shared" si="7"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="L207">
         <v>4</v>
@@ -17277,30 +17273,30 @@
         <v>33</v>
       </c>
       <c r="H208">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I208" s="2">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J208" s="2">
         <f t="shared" si="7"/>
-        <v>61.25</v>
+        <v>63</v>
       </c>
       <c r="K208" t="s">
         <v>234</v>
       </c>
       <c r="L208">
+        <v>8</v>
+      </c>
+      <c r="M208">
+        <v>6.56</v>
+      </c>
+      <c r="N208">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="O208">
         <v>7</v>
-      </c>
-      <c r="M208">
-        <v>6.5</v>
-      </c>
-      <c r="N208">
-        <v>9</v>
-      </c>
-      <c r="O208">
-        <v>6</v>
       </c>
       <c r="P208">
         <v>0</v>
@@ -17423,15 +17419,15 @@
         <v>34</v>
       </c>
       <c r="H210">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I210" s="2">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J210" s="2">
         <f t="shared" si="7"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K210" t="s">
         <v>234</v>
@@ -17496,24 +17492,24 @@
         <v>42</v>
       </c>
       <c r="H211">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I211" s="2">
         <f t="shared" si="6"/>
-        <v>2.8000000000000003</v>
+        <v>3</v>
       </c>
       <c r="J211" s="2">
         <f t="shared" si="7"/>
-        <v>24.5</v>
+        <v>26.25</v>
       </c>
       <c r="L211">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M211">
-        <v>6.57</v>
+        <v>6.56</v>
       </c>
       <c r="N211">
-        <v>7.43</v>
+        <v>7.31</v>
       </c>
       <c r="O211">
         <v>1</v>
@@ -17566,27 +17562,27 @@
         <v>33</v>
       </c>
       <c r="H212">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I212" s="2">
         <f t="shared" si="6"/>
-        <v>3.4000000000000004</v>
+        <v>3.2</v>
       </c>
       <c r="J212" s="2">
         <f t="shared" si="7"/>
-        <v>29.75</v>
+        <v>28</v>
       </c>
       <c r="K212" t="s">
         <v>180</v>
       </c>
       <c r="L212">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M212">
-        <v>5.93</v>
+        <v>5.88</v>
       </c>
       <c r="N212">
-        <v>6.14</v>
+        <v>6.06</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -17639,15 +17635,15 @@
         <v>78</v>
       </c>
       <c r="H213">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I213" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J213" s="2">
         <f t="shared" si="7"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="K213" t="s">
         <v>127</v>
@@ -17793,13 +17789,13 @@
         <v>8.75</v>
       </c>
       <c r="L215">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M215">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="N215">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="O215">
         <v>0</v>
@@ -17852,27 +17848,27 @@
         <v>29</v>
       </c>
       <c r="H216">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I216" s="2">
         <f t="shared" si="6"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J216" s="2">
         <f t="shared" si="7"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
       <c r="K216" t="s">
         <v>27</v>
       </c>
       <c r="L216">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M216">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="N216">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="O216">
         <v>0</v>
@@ -17998,24 +17994,24 @@
         <v>47</v>
       </c>
       <c r="H218">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I218" s="2">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J218" s="2">
         <f t="shared" si="7"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="L218">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M218">
-        <v>5.62</v>
+        <v>5.5</v>
       </c>
       <c r="N218">
-        <v>5.62</v>
+        <v>5.5</v>
       </c>
       <c r="O218">
         <v>0</v>
@@ -18068,27 +18064,27 @@
         <v>45</v>
       </c>
       <c r="H219">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I219" s="2">
         <f t="shared" si="6"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J219" s="2">
         <f t="shared" si="7"/>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
       <c r="K219" t="s">
         <v>156</v>
       </c>
       <c r="L219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M219">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="N219">
-        <v>7.1</v>
+        <v>6.92</v>
       </c>
       <c r="O219">
         <v>1</v>
@@ -18141,27 +18137,27 @@
         <v>91</v>
       </c>
       <c r="H220">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I220" s="2">
         <f t="shared" si="6"/>
-        <v>2.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J220" s="2">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="K220" t="s">
         <v>156</v>
       </c>
       <c r="L220">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M220">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="N220">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="O220">
         <v>1</v>
@@ -18214,15 +18210,15 @@
         <v>33</v>
       </c>
       <c r="H221">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I221" s="2">
         <f t="shared" si="6"/>
-        <v>2.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J221" s="2">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="L221">
         <v>4</v>
@@ -18295,13 +18291,13 @@
         <v>8.75</v>
       </c>
       <c r="L222">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M222">
-        <v>5.67</v>
+        <v>5.64</v>
       </c>
       <c r="N222">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="O222">
         <v>0</v>
@@ -18365,13 +18361,13 @@
         <v>10.5</v>
       </c>
       <c r="L223">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M223">
         <v>5.56</v>
       </c>
       <c r="N223">
-        <v>5.56</v>
+        <v>5.67</v>
       </c>
       <c r="O223">
         <v>0</v>
@@ -18392,7 +18388,7 @@
         <v>0</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V223">
         <v>0</v>
@@ -18564,27 +18560,27 @@
         <v>60</v>
       </c>
       <c r="H226">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I226" s="2">
         <f t="shared" si="6"/>
-        <v>3.8000000000000003</v>
+        <v>4</v>
       </c>
       <c r="J226" s="2">
         <f t="shared" si="7"/>
-        <v>33.25</v>
+        <v>35</v>
       </c>
       <c r="K226" t="s">
         <v>265</v>
       </c>
       <c r="L226">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M226">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
       <c r="N226">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="O226">
         <v>3</v>
@@ -18707,27 +18703,27 @@
         <v>78</v>
       </c>
       <c r="H228">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I228" s="2">
         <f t="shared" si="6"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J228" s="2">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K228" t="s">
         <v>234</v>
       </c>
       <c r="L228">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M228">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="N228">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="O228">
         <v>0</v>
@@ -18780,15 +18776,15 @@
         <v>183</v>
       </c>
       <c r="H229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I229" s="2">
         <f t="shared" si="6"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="J229" s="2">
         <f t="shared" si="7"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="L229">
         <v>0</v>
@@ -18864,13 +18860,13 @@
         <v>156</v>
       </c>
       <c r="L230">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M230">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="N230">
-        <v>5.62</v>
+        <v>5.72</v>
       </c>
       <c r="O230">
         <v>0</v>
@@ -18923,21 +18919,21 @@
         <v>39</v>
       </c>
       <c r="H231">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I231" s="2">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J231" s="2">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="L231">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M231">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="N231">
         <v>5</v>
@@ -19074,13 +19070,13 @@
         <v>19.25</v>
       </c>
       <c r="L233">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M233">
-        <v>6.3</v>
+        <v>6.17</v>
       </c>
       <c r="N233">
-        <v>7.7</v>
+        <v>7.25</v>
       </c>
       <c r="O233">
         <v>2</v>
@@ -19104,7 +19100,7 @@
         <v>1</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W233">
         <v>0</v>
@@ -19133,27 +19129,27 @@
         <v>47</v>
       </c>
       <c r="H234">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I234" s="2">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J234" s="2">
         <f t="shared" si="7"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="K234" t="s">
         <v>127</v>
       </c>
       <c r="L234">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M234">
-        <v>5.81</v>
+        <v>5.89</v>
       </c>
       <c r="N234">
-        <v>5.81</v>
+        <v>5.89</v>
       </c>
       <c r="O234">
         <v>0</v>
@@ -19220,13 +19216,13 @@
         <v>27</v>
       </c>
       <c r="L235">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M235">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="N235">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="O235">
         <v>2</v>
@@ -19279,15 +19275,15 @@
         <v>100</v>
       </c>
       <c r="H236">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I236" s="2">
         <f t="shared" si="6"/>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J236" s="2">
         <f t="shared" si="7"/>
-        <v>19.25</v>
+        <v>17.5</v>
       </c>
       <c r="K236" t="s">
         <v>30</v>
@@ -19503,13 +19499,13 @@
         <v>7</v>
       </c>
       <c r="L239">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M239">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="N239">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -19562,27 +19558,27 @@
         <v>91</v>
       </c>
       <c r="H240">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I240" s="2">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
+        <v>2</v>
       </c>
       <c r="J240" s="2">
         <f t="shared" si="7"/>
-        <v>12.25</v>
+        <v>17.5</v>
       </c>
       <c r="L240">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M240">
-        <v>5.8</v>
+        <v>6.08</v>
       </c>
       <c r="N240">
-        <v>5.8</v>
+        <v>6.75</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P240">
         <v>0</v>
@@ -19600,7 +19596,7 @@
         <v>0</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V240">
         <v>0</v>
@@ -19632,24 +19628,24 @@
         <v>34</v>
       </c>
       <c r="H241">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I241" s="2">
         <f t="shared" si="6"/>
-        <v>1.2000000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J241" s="2">
         <f t="shared" si="7"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="L241">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M241">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="N241">
-        <v>8.75</v>
+        <v>7.67</v>
       </c>
       <c r="O241">
         <v>1</v>
@@ -19786,13 +19782,13 @@
         <v>14</v>
       </c>
       <c r="L243">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M243">
+        <v>5.83</v>
+      </c>
+      <c r="N243">
         <v>5.94</v>
-      </c>
-      <c r="N243">
-        <v>6.06</v>
       </c>
       <c r="O243">
         <v>0</v>
@@ -19856,10 +19852,10 @@
         <v>8.75</v>
       </c>
       <c r="L244">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M244">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="N244">
         <v>6</v>
@@ -19915,15 +19911,15 @@
         <v>26</v>
       </c>
       <c r="H245">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I245" s="2">
         <f t="shared" si="6"/>
-        <v>3.6</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J245" s="2">
         <f t="shared" si="7"/>
-        <v>31.5</v>
+        <v>29.75</v>
       </c>
       <c r="K245" t="s">
         <v>30</v>
@@ -19988,27 +19984,27 @@
         <v>45</v>
       </c>
       <c r="H246">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I246" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J246" s="2">
         <f t="shared" si="7"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="K246" t="s">
         <v>265</v>
       </c>
       <c r="L246">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M246">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="N246">
-        <v>6.21</v>
+        <v>5.94</v>
       </c>
       <c r="O246">
         <v>1</v>
@@ -20035,7 +20031,7 @@
         <v>1</v>
       </c>
       <c r="W246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X246">
         <v>0</v>
@@ -20142,13 +20138,13 @@
         <v>19.25</v>
       </c>
       <c r="L248">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M248">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
       <c r="N248">
-        <v>6.31</v>
+        <v>6.22</v>
       </c>
       <c r="O248">
         <v>1</v>
@@ -20212,13 +20208,13 @@
         <v>17.5</v>
       </c>
       <c r="L249">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M249">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="N249">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="O249">
         <v>0</v>
@@ -20285,13 +20281,13 @@
         <v>265</v>
       </c>
       <c r="L250">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M250">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="N250">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="O250">
         <v>0</v>
@@ -20355,13 +20351,13 @@
         <v>5.25</v>
       </c>
       <c r="L251">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M251">
-        <v>5.67</v>
+        <v>5.88</v>
       </c>
       <c r="N251">
-        <v>5.67</v>
+        <v>5.88</v>
       </c>
       <c r="O251">
         <v>0</v>
@@ -20484,27 +20480,27 @@
         <v>152</v>
       </c>
       <c r="H253">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I253" s="2">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J253" s="2">
         <f t="shared" si="7"/>
-        <v>26.25</v>
+        <v>28</v>
       </c>
       <c r="K253" t="s">
         <v>30</v>
       </c>
       <c r="L253">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M253">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="N253">
-        <v>8.08</v>
+        <v>7.86</v>
       </c>
       <c r="O253">
         <v>2</v>
@@ -20557,27 +20553,27 @@
         <v>91</v>
       </c>
       <c r="H254">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I254" s="2">
         <f t="shared" si="6"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J254" s="2">
         <f t="shared" si="7"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
       <c r="K254" t="s">
         <v>265</v>
       </c>
       <c r="L254">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M254">
-        <v>5.9</v>
+        <v>5.83</v>
       </c>
       <c r="N254">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="O254">
         <v>1</v>
@@ -20700,15 +20696,15 @@
         <v>60</v>
       </c>
       <c r="H256">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I256" s="2">
         <f t="shared" si="6"/>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J256" s="2">
         <f t="shared" si="7"/>
-        <v>19.25</v>
+        <v>17.5</v>
       </c>
       <c r="L256">
         <v>5</v>
@@ -20983,15 +20979,15 @@
         <v>47</v>
       </c>
       <c r="H260">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I260" s="2">
         <f t="shared" si="8"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J260" s="2">
         <f t="shared" si="9"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="L260">
         <v>5</v>
@@ -21053,27 +21049,27 @@
         <v>33</v>
       </c>
       <c r="H261">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I261" s="2">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J261" s="2">
         <f t="shared" si="9"/>
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="K261" t="s">
         <v>234</v>
       </c>
       <c r="L261">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M261">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="N261">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="O261">
         <v>1</v>
@@ -21199,24 +21195,24 @@
         <v>29</v>
       </c>
       <c r="H263">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I263" s="2">
         <f t="shared" si="8"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="J263" s="2">
         <f t="shared" si="9"/>
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="L263">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M263">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="N263">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="O263">
         <v>0</v>
@@ -21269,30 +21265,30 @@
         <v>60</v>
       </c>
       <c r="H264">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I264" s="2">
         <f t="shared" si="8"/>
-        <v>2.8000000000000003</v>
+        <v>3.2</v>
       </c>
       <c r="J264" s="2">
         <f t="shared" si="9"/>
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="K264" t="s">
         <v>95</v>
       </c>
       <c r="L264">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M264">
-        <v>5.81</v>
+        <v>6</v>
       </c>
       <c r="N264">
-        <v>5.94</v>
+        <v>6.56</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P264">
         <v>0</v>
@@ -21310,7 +21306,7 @@
         <v>0</v>
       </c>
       <c r="U264">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V264">
         <v>0</v>
@@ -21628,27 +21624,27 @@
         <v>225</v>
       </c>
       <c r="H269">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I269" s="2">
         <f t="shared" si="8"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J269" s="2">
         <f t="shared" si="9"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="K269" t="s">
         <v>30</v>
       </c>
       <c r="L269">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M269">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="N269">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="O269">
         <v>1</v>
@@ -21701,24 +21697,24 @@
         <v>78</v>
       </c>
       <c r="H270">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I270" s="2">
         <f t="shared" si="8"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J270" s="2">
         <f t="shared" si="9"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="L270">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M270">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="N270">
-        <v>6.43</v>
+        <v>6.31</v>
       </c>
       <c r="O270">
         <v>1</v>
@@ -21782,13 +21778,13 @@
         <v>3.5</v>
       </c>
       <c r="L271">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M271">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N271">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O271">
         <v>0</v>
@@ -21852,7 +21848,7 @@
         <v>3.5</v>
       </c>
       <c r="L272">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M272">
         <v>6</v>
@@ -21911,27 +21907,27 @@
         <v>34</v>
       </c>
       <c r="H273">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I273" s="2">
         <f t="shared" si="8"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J273" s="2">
         <f t="shared" si="9"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K273" t="s">
         <v>265</v>
       </c>
       <c r="L273">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M273">
-        <v>5.93</v>
+        <v>5.88</v>
       </c>
       <c r="N273">
-        <v>5.79</v>
+        <v>5.75</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -21984,15 +21980,15 @@
         <v>34</v>
       </c>
       <c r="H274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I274" s="2">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J274" s="2">
         <f t="shared" si="9"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K274" t="s">
         <v>30</v>
@@ -22057,27 +22053,27 @@
         <v>39</v>
       </c>
       <c r="H275">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I275" s="2">
         <f t="shared" si="8"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J275" s="2">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="L275">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M275">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="N275">
-        <v>5.62</v>
+        <v>6.4</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P275">
         <v>0</v>
@@ -22127,30 +22123,30 @@
         <v>33</v>
       </c>
       <c r="H276">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I276" s="2">
         <f t="shared" si="8"/>
-        <v>4.8000000000000007</v>
+        <v>5</v>
       </c>
       <c r="J276" s="2">
         <f t="shared" si="9"/>
-        <v>42</v>
+        <v>43.75</v>
       </c>
       <c r="K276" t="s">
         <v>30</v>
       </c>
       <c r="L276">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M276">
-        <v>6.19</v>
+        <v>6.28</v>
       </c>
       <c r="N276">
-        <v>6.94</v>
+        <v>7.28</v>
       </c>
       <c r="O276">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P276">
         <v>0</v>
@@ -22270,27 +22266,27 @@
         <v>60</v>
       </c>
       <c r="H278">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I278" s="2">
         <f t="shared" si="8"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J278" s="2">
         <f t="shared" si="9"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K278" t="s">
         <v>27</v>
       </c>
       <c r="L278">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M278">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="N278">
-        <v>6.19</v>
+        <v>6.11</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -22424,13 +22420,13 @@
         <v>7</v>
       </c>
       <c r="L280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M280">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="N280">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="O280">
         <v>0</v>
@@ -22483,24 +22479,24 @@
         <v>42</v>
       </c>
       <c r="H281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I281" s="2">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J281" s="2">
         <f t="shared" si="9"/>
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="L281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M281">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="N281">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O281">
         <v>0</v>
@@ -22553,27 +22549,27 @@
         <v>47</v>
       </c>
       <c r="H282">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I282" s="2">
         <f t="shared" si="8"/>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J282" s="2">
         <f t="shared" si="9"/>
-        <v>19.25</v>
+        <v>17.5</v>
       </c>
       <c r="K282" t="s">
         <v>127</v>
       </c>
       <c r="L282">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M282">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="N282">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="O282">
         <v>0</v>
@@ -22637,13 +22633,13 @@
         <v>8.75</v>
       </c>
       <c r="L283">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M283">
-        <v>5.58</v>
+        <v>5.71</v>
       </c>
       <c r="N283">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="O283">
         <v>0</v>
@@ -22707,10 +22703,10 @@
         <v>10.5</v>
       </c>
       <c r="L284">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M284">
-        <v>5.75</v>
+        <v>5.79</v>
       </c>
       <c r="N284">
         <v>6</v>
@@ -22836,30 +22832,30 @@
         <v>62</v>
       </c>
       <c r="H286">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I286" s="2">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J286" s="2">
         <f t="shared" si="9"/>
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="K286" t="s">
         <v>180</v>
       </c>
       <c r="L286">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M286">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="N286">
-        <v>7</v>
+        <v>7.36</v>
       </c>
       <c r="O286">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P286">
         <v>0</v>
@@ -22909,24 +22905,24 @@
         <v>47</v>
       </c>
       <c r="H287">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I287" s="2">
         <f t="shared" si="8"/>
-        <v>1.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J287" s="2">
         <f t="shared" si="9"/>
-        <v>15.75</v>
+        <v>19.25</v>
       </c>
       <c r="L287">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M287">
-        <v>6.36</v>
+        <v>6.44</v>
       </c>
       <c r="N287">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="O287">
         <v>0</v>
@@ -22979,15 +22975,15 @@
         <v>34</v>
       </c>
       <c r="H288">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I288" s="2">
         <f t="shared" si="8"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J288" s="2">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="K288" t="s">
         <v>127</v>
@@ -23052,24 +23048,24 @@
         <v>41</v>
       </c>
       <c r="H289">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I289" s="2">
         <f t="shared" si="8"/>
-        <v>2.8000000000000003</v>
+        <v>3.2</v>
       </c>
       <c r="J289" s="2">
         <f t="shared" si="9"/>
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="L289">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M289">
-        <v>6.69</v>
+        <v>6.83</v>
       </c>
       <c r="N289">
-        <v>7.81</v>
+        <v>8.06</v>
       </c>
       <c r="O289">
         <v>3</v>
@@ -23090,7 +23086,7 @@
         <v>0</v>
       </c>
       <c r="U289">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V289">
         <v>2</v>
@@ -23133,13 +23129,13 @@
         <v>7</v>
       </c>
       <c r="L290">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M290">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="N290">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="O290">
         <v>0</v>
@@ -23192,15 +23188,15 @@
         <v>41</v>
       </c>
       <c r="H291">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I291" s="2">
         <f t="shared" si="8"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J291" s="2">
         <f t="shared" si="9"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="L291">
         <v>4</v>
@@ -23416,13 +23412,13 @@
         <v>156</v>
       </c>
       <c r="L294">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M294">
-        <v>6.14</v>
+        <v>6.06</v>
       </c>
       <c r="N294">
-        <v>6.57</v>
+        <v>6.44</v>
       </c>
       <c r="O294">
         <v>1</v>
@@ -23685,24 +23681,24 @@
         <v>33</v>
       </c>
       <c r="H298">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I298" s="2">
         <f t="shared" si="8"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J298" s="2">
         <f t="shared" si="9"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="L298">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M298">
-        <v>5.69</v>
+        <v>5.61</v>
       </c>
       <c r="N298">
-        <v>5.81</v>
+        <v>5.72</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -23755,21 +23751,21 @@
         <v>39</v>
       </c>
       <c r="H299">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I299" s="2">
         <f t="shared" si="8"/>
-        <v>2.4000000000000004</v>
+        <v>2.6</v>
       </c>
       <c r="J299" s="2">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="L299">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M299">
-        <v>6.38</v>
+        <v>6.39</v>
       </c>
       <c r="N299">
         <v>6.44</v>
@@ -24116,13 +24112,13 @@
         <v>5.25</v>
       </c>
       <c r="L304">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M304">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="N304">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O304">
         <v>0</v>
@@ -24186,19 +24182,19 @@
         <v>15.75</v>
       </c>
       <c r="L305">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M305">
-        <v>6.31</v>
+        <v>6.28</v>
       </c>
       <c r="N305">
-        <v>4.5599999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="O305">
         <v>0</v>
       </c>
       <c r="P305">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q305">
         <v>1</v>
@@ -24399,13 +24395,13 @@
         <v>30</v>
       </c>
       <c r="L308">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M308">
-        <v>6.36</v>
+        <v>6.31</v>
       </c>
       <c r="N308">
-        <v>6.93</v>
+        <v>6.81</v>
       </c>
       <c r="O308">
         <v>0</v>
@@ -24458,27 +24454,27 @@
         <v>62</v>
       </c>
       <c r="H309">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I309" s="2">
         <f t="shared" si="8"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J309" s="2">
         <f t="shared" si="9"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K309" t="s">
         <v>127</v>
       </c>
       <c r="L309">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M309">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="N309">
-        <v>5.75</v>
+        <v>5.72</v>
       </c>
       <c r="O309">
         <v>0</v>
@@ -24531,24 +24527,24 @@
         <v>34</v>
       </c>
       <c r="H310">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I310" s="2">
         <f t="shared" si="8"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J310" s="2">
         <f t="shared" si="9"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="L310">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M310">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="N310">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="O310">
         <v>0</v>
@@ -24674,30 +24670,30 @@
         <v>26</v>
       </c>
       <c r="H312">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I312" s="2">
         <f t="shared" si="8"/>
-        <v>1.4000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J312" s="2">
         <f t="shared" si="9"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="L312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M312">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="N312">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O312">
         <v>0</v>
       </c>
       <c r="P312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q312">
         <v>0</v>
@@ -24744,15 +24740,15 @@
         <v>56</v>
       </c>
       <c r="H313">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I313" s="2">
         <f t="shared" si="8"/>
-        <v>3.4000000000000004</v>
+        <v>3.2</v>
       </c>
       <c r="J313" s="2">
         <f t="shared" si="9"/>
-        <v>29.75</v>
+        <v>28</v>
       </c>
       <c r="K313" t="s">
         <v>30</v>
@@ -24817,27 +24813,27 @@
         <v>33</v>
       </c>
       <c r="H314">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I314" s="2">
         <f t="shared" si="8"/>
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="J314" s="2">
         <f t="shared" si="9"/>
-        <v>38.5</v>
+        <v>35</v>
       </c>
       <c r="K314" t="s">
         <v>265</v>
       </c>
       <c r="L314">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M314">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="N314">
-        <v>6.44</v>
+        <v>6.28</v>
       </c>
       <c r="O314">
         <v>2</v>
@@ -24890,30 +24886,30 @@
         <v>41</v>
       </c>
       <c r="H315">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I315" s="2">
         <f t="shared" si="8"/>
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J315" s="2">
         <f t="shared" si="9"/>
-        <v>22.75</v>
+        <v>26.25</v>
       </c>
       <c r="K315" t="s">
         <v>27</v>
       </c>
       <c r="L315">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M315">
-        <v>6.21</v>
+        <v>6.44</v>
       </c>
       <c r="N315">
-        <v>7</v>
+        <v>7.62</v>
       </c>
       <c r="O315">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P315">
         <v>0</v>
@@ -24931,7 +24927,7 @@
         <v>0</v>
       </c>
       <c r="U315">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V315">
         <v>1</v>
@@ -25106,30 +25102,30 @@
         <v>26</v>
       </c>
       <c r="H318">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I318" s="2">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J318" s="2">
         <f t="shared" si="9"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="L318">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M318">
         <v>6.56</v>
       </c>
       <c r="N318">
-        <v>4.9400000000000004</v>
+        <v>5</v>
       </c>
       <c r="O318">
         <v>0</v>
       </c>
       <c r="P318">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q318">
         <v>0</v>
@@ -25316,15 +25312,15 @@
         <v>60</v>
       </c>
       <c r="H321">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I321" s="2">
         <f t="shared" si="8"/>
-        <v>3.4000000000000004</v>
+        <v>3.2</v>
       </c>
       <c r="J321" s="2">
         <f t="shared" si="9"/>
-        <v>29.75</v>
+        <v>28</v>
       </c>
       <c r="K321" t="s">
         <v>180</v>
@@ -25403,13 +25399,13 @@
         <v>30</v>
       </c>
       <c r="L322">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M322">
-        <v>6.38</v>
+        <v>6.28</v>
       </c>
       <c r="N322">
-        <v>8.81</v>
+        <v>8.44</v>
       </c>
       <c r="O322">
         <v>6</v>
@@ -25462,27 +25458,27 @@
         <v>26</v>
       </c>
       <c r="H323">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I323" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J323" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>14</v>
       </c>
       <c r="K323" t="s">
         <v>156</v>
       </c>
       <c r="L323">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M323">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="N323">
-        <v>3.75</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="O323">
         <v>0</v>
@@ -25491,7 +25487,7 @@
         <v>18</v>
       </c>
       <c r="Q323">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R323">
         <v>0</v>
@@ -25549,19 +25545,19 @@
         <v>265</v>
       </c>
       <c r="L324">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M324">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="N324">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="O324">
         <v>0</v>
       </c>
       <c r="P324">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q324">
         <v>1</v>
@@ -25608,15 +25604,15 @@
         <v>78</v>
       </c>
       <c r="H325">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I325" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J325" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K325" t="s">
         <v>95</v>
@@ -25695,13 +25691,13 @@
         <v>95</v>
       </c>
       <c r="L326">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M326">
-        <v>5.86</v>
+        <v>5.81</v>
       </c>
       <c r="N326">
-        <v>6.21</v>
+        <v>6.12</v>
       </c>
       <c r="O326">
         <v>1</v>
@@ -25754,27 +25750,27 @@
         <v>42</v>
       </c>
       <c r="H327">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I327" s="2">
         <f t="shared" si="10"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J327" s="2">
         <f t="shared" si="11"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="K327" t="s">
         <v>95</v>
       </c>
       <c r="L327">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M327">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="N327">
-        <v>6.33</v>
+        <v>5.5</v>
       </c>
       <c r="O327">
         <v>0</v>
@@ -25804,7 +25800,7 @@
         <v>0</v>
       </c>
       <c r="X327">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:24" x14ac:dyDescent="0.2">
@@ -25841,13 +25837,13 @@
         <v>180</v>
       </c>
       <c r="L328">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M328">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="N328">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O328">
         <v>0</v>
@@ -25900,24 +25896,24 @@
         <v>108</v>
       </c>
       <c r="H329">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I329" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J329" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="L329">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M329">
-        <v>6.1</v>
+        <v>6.08</v>
       </c>
       <c r="N329">
-        <v>6.1</v>
+        <v>6.08</v>
       </c>
       <c r="O329">
         <v>0</v>
@@ -25984,13 +25980,13 @@
         <v>265</v>
       </c>
       <c r="L330">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M330">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N330">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O330">
         <v>0</v>
@@ -26113,24 +26109,24 @@
         <v>41</v>
       </c>
       <c r="H332">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I332" s="2">
         <f t="shared" si="10"/>
-        <v>2.6</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J332" s="2">
         <f t="shared" si="11"/>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="L332">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M332">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
       <c r="N332">
-        <v>7.08</v>
+        <v>7.14</v>
       </c>
       <c r="O332">
         <v>0</v>
@@ -26151,7 +26147,7 @@
         <v>0</v>
       </c>
       <c r="U332">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V332">
         <v>0</v>
@@ -26183,27 +26179,27 @@
         <v>183</v>
       </c>
       <c r="H333">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I333" s="2">
         <f t="shared" si="10"/>
-        <v>2.8000000000000003</v>
+        <v>3</v>
       </c>
       <c r="J333" s="2">
         <f t="shared" si="11"/>
-        <v>24.5</v>
+        <v>26.25</v>
       </c>
       <c r="K333" t="s">
         <v>180</v>
       </c>
       <c r="L333">
+        <v>8</v>
+      </c>
+      <c r="M333">
+        <v>6.06</v>
+      </c>
+      <c r="N333">
         <v>7</v>
-      </c>
-      <c r="M333">
-        <v>6</v>
-      </c>
-      <c r="N333">
-        <v>6.93</v>
       </c>
       <c r="O333">
         <v>2</v>
@@ -26224,7 +26220,7 @@
         <v>0</v>
       </c>
       <c r="U333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V333">
         <v>1</v>
@@ -26256,30 +26252,30 @@
         <v>26</v>
       </c>
       <c r="H334">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I334" s="2">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J334" s="2">
         <f t="shared" si="11"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="L334">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M334">
         <v>6</v>
       </c>
       <c r="N334">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="O334">
         <v>0</v>
       </c>
       <c r="P334">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -26326,24 +26322,24 @@
         <v>78</v>
       </c>
       <c r="H335">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I335" s="2">
         <f t="shared" si="10"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J335" s="2">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="L335">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M335">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="N335">
-        <v>7.67</v>
+        <v>6.88</v>
       </c>
       <c r="O335">
         <v>1</v>
@@ -26367,7 +26363,7 @@
         <v>0</v>
       </c>
       <c r="V335">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W335">
         <v>0</v>
@@ -26466,27 +26462,27 @@
         <v>60</v>
       </c>
       <c r="H337">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I337" s="2">
         <f t="shared" si="10"/>
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J337" s="2">
         <f t="shared" si="11"/>
-        <v>22.75</v>
+        <v>28</v>
       </c>
       <c r="L337">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M337">
-        <v>6.42</v>
+        <v>6.64</v>
       </c>
       <c r="N337">
-        <v>7.75</v>
+        <v>8.64</v>
       </c>
       <c r="O337">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P337">
         <v>0</v>
@@ -26620,13 +26616,13 @@
         <v>234</v>
       </c>
       <c r="L339">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M339">
-        <v>6.25</v>
+        <v>6.14</v>
       </c>
       <c r="N339">
-        <v>6.75</v>
+        <v>6.57</v>
       </c>
       <c r="O339">
         <v>1</v>
@@ -26749,24 +26745,24 @@
         <v>62</v>
       </c>
       <c r="H341">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I341" s="2">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J341" s="2">
         <f t="shared" si="11"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="L341">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M341">
+        <v>5.88</v>
+      </c>
+      <c r="N341">
         <v>6</v>
-      </c>
-      <c r="N341">
-        <v>6.14</v>
       </c>
       <c r="O341">
         <v>0</v>
@@ -26959,30 +26955,30 @@
         <v>36</v>
       </c>
       <c r="H344">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I344" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J344" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>15.75</v>
       </c>
       <c r="K344" t="s">
         <v>265</v>
       </c>
       <c r="L344">
+        <v>5</v>
+      </c>
+      <c r="M344">
+        <v>6.5</v>
+      </c>
+      <c r="N344">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="O344">
         <v>4</v>
-      </c>
-      <c r="M344">
-        <v>6.25</v>
-      </c>
-      <c r="N344">
-        <v>7.62</v>
-      </c>
-      <c r="O344">
-        <v>2</v>
       </c>
       <c r="P344">
         <v>0</v>
@@ -27032,24 +27028,24 @@
         <v>45</v>
       </c>
       <c r="H345">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I345" s="2">
         <f t="shared" si="10"/>
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J345" s="2">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="L345">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M345">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="N345">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="O345">
         <v>1</v>
@@ -27070,7 +27066,7 @@
         <v>0</v>
       </c>
       <c r="U345">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V345">
         <v>0</v>
@@ -27102,24 +27098,24 @@
         <v>34</v>
       </c>
       <c r="H346">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I346" s="2">
         <f t="shared" si="10"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J346" s="2">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="L346">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M346">
-        <v>6.17</v>
+        <v>6.25</v>
       </c>
       <c r="N346">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="O346">
         <v>0</v>
@@ -27140,7 +27136,7 @@
         <v>0</v>
       </c>
       <c r="U346">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V346">
         <v>1</v>
@@ -27172,15 +27168,15 @@
         <v>34</v>
       </c>
       <c r="H347">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I347" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J347" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L347">
         <v>6</v>
@@ -27242,27 +27238,27 @@
         <v>34</v>
       </c>
       <c r="H348">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I348" s="2">
         <f t="shared" si="10"/>
-        <v>0.60000000000000009</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J348" s="2">
         <f t="shared" si="11"/>
-        <v>5.25</v>
+        <v>10.5</v>
       </c>
       <c r="L348">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M348">
-        <v>5.71</v>
+        <v>5.81</v>
       </c>
       <c r="N348">
-        <v>5.57</v>
+        <v>6.06</v>
       </c>
       <c r="O348">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P348">
         <v>0</v>
@@ -27452,27 +27448,27 @@
         <v>34</v>
       </c>
       <c r="H351">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I351" s="2">
         <f t="shared" si="10"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J351" s="2">
         <f t="shared" si="11"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
       <c r="K351" t="s">
         <v>234</v>
       </c>
       <c r="L351">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M351">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="N351">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="O351">
         <v>0</v>
@@ -27595,30 +27591,30 @@
         <v>60</v>
       </c>
       <c r="H353">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I353" s="2">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J353" s="2">
         <f t="shared" si="11"/>
-        <v>26.25</v>
+        <v>29.75</v>
       </c>
       <c r="K353" t="s">
         <v>27</v>
       </c>
       <c r="L353">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M353">
-        <v>6.58</v>
+        <v>6.64</v>
       </c>
       <c r="N353">
-        <v>8.08</v>
+        <v>8.36</v>
       </c>
       <c r="O353">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P353">
         <v>0</v>
@@ -27749,13 +27745,13 @@
         <v>5.25</v>
       </c>
       <c r="L355">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M355">
         <v>5.5</v>
       </c>
       <c r="N355">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="O355">
         <v>0</v>
@@ -27822,13 +27818,13 @@
         <v>30</v>
       </c>
       <c r="L356">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M356">
+        <v>5.56</v>
+      </c>
+      <c r="N356">
         <v>5.5</v>
-      </c>
-      <c r="N356">
-        <v>5.44</v>
       </c>
       <c r="O356">
         <v>0</v>
@@ -28038,13 +28034,13 @@
         <v>127</v>
       </c>
       <c r="L359">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M359">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="N359">
-        <v>5.62</v>
+        <v>5.72</v>
       </c>
       <c r="O359">
         <v>0</v>
@@ -28097,27 +28093,27 @@
         <v>62</v>
       </c>
       <c r="H360">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I360" s="2">
         <f t="shared" si="10"/>
-        <v>1.2000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="J360" s="2">
         <f t="shared" si="11"/>
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="K360" t="s">
         <v>234</v>
       </c>
       <c r="L360">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M360">
-        <v>5.75</v>
+        <v>5.64</v>
       </c>
       <c r="N360">
-        <v>5.75</v>
+        <v>5.21</v>
       </c>
       <c r="O360">
         <v>0</v>
@@ -28129,13 +28125,13 @@
         <v>0</v>
       </c>
       <c r="R360">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S360">
         <v>0</v>
       </c>
       <c r="T360">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U360">
         <v>0</v>
@@ -28184,13 +28180,13 @@
         <v>95</v>
       </c>
       <c r="L361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M361">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="N361">
-        <v>7.6</v>
+        <v>7.25</v>
       </c>
       <c r="O361">
         <v>2</v>
@@ -28456,15 +28452,15 @@
         <v>33</v>
       </c>
       <c r="H365">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I365" s="2">
         <f t="shared" si="10"/>
-        <v>2.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J365" s="2">
         <f t="shared" si="11"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="L365">
         <v>4</v>
@@ -28683,13 +28679,13 @@
         <v>17.5</v>
       </c>
       <c r="L368">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M368">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
       <c r="N368">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="O368">
         <v>1</v>
@@ -28713,7 +28709,7 @@
         <v>0</v>
       </c>
       <c r="V368">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W368">
         <v>0</v>
@@ -28896,13 +28892,13 @@
         <v>234</v>
       </c>
       <c r="L371">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M371">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="N371">
-        <v>7.38</v>
+        <v>7.22</v>
       </c>
       <c r="O371">
         <v>3</v>
@@ -29025,27 +29021,27 @@
         <v>39</v>
       </c>
       <c r="H373">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I373" s="2">
         <f t="shared" si="10"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J373" s="2">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="K373" t="s">
         <v>95</v>
       </c>
       <c r="L373">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M373">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="N373">
-        <v>5.93</v>
+        <v>6.12</v>
       </c>
       <c r="O373">
         <v>0</v>
@@ -29066,7 +29062,7 @@
         <v>0</v>
       </c>
       <c r="U373">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V373">
         <v>2</v>
@@ -29098,27 +29094,27 @@
         <v>60</v>
       </c>
       <c r="H374">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I374" s="2">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J374" s="2">
         <f t="shared" si="11"/>
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="K374" t="s">
         <v>234</v>
       </c>
       <c r="L374">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M374">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="N374">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="O374">
         <v>0</v>
@@ -29171,15 +29167,15 @@
         <v>29</v>
       </c>
       <c r="H375">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I375" s="2">
         <f t="shared" si="10"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J375" s="2">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="K375" t="s">
         <v>265</v>
@@ -29244,15 +29240,15 @@
         <v>91</v>
       </c>
       <c r="H376">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I376" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J376" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K376" t="s">
         <v>95</v>
@@ -29317,24 +29313,24 @@
         <v>34</v>
       </c>
       <c r="H377">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I377" s="2">
         <f t="shared" si="10"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J377" s="2">
         <f t="shared" si="11"/>
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="L377">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M377">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N377">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O377">
         <v>0</v>
@@ -29530,24 +29526,24 @@
         <v>108</v>
       </c>
       <c r="H380">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I380" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J380" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L380">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M380">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="N380">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="O380">
         <v>0</v>
@@ -29600,24 +29596,24 @@
         <v>39</v>
       </c>
       <c r="H381">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I381" s="2">
         <f t="shared" si="10"/>
-        <v>2.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J381" s="2">
         <f t="shared" si="11"/>
-        <v>19.25</v>
+        <v>21</v>
       </c>
       <c r="L381">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M381">
         <v>6</v>
       </c>
       <c r="N381">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="O381">
         <v>2</v>
@@ -29810,30 +29806,30 @@
         <v>41</v>
       </c>
       <c r="H384">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I384" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J384" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>14</v>
       </c>
       <c r="K384" t="s">
         <v>127</v>
       </c>
       <c r="L384">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M384">
-        <v>5.86</v>
+        <v>6.06</v>
       </c>
       <c r="N384">
-        <v>5.79</v>
+        <v>6.5</v>
       </c>
       <c r="O384">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P384">
         <v>0</v>
@@ -29851,7 +29847,7 @@
         <v>0</v>
       </c>
       <c r="U384">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V384">
         <v>1</v>
@@ -29883,15 +29879,15 @@
         <v>41</v>
       </c>
       <c r="H385">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I385" s="2">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J385" s="2">
         <f t="shared" si="11"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K385" t="s">
         <v>234</v>
@@ -29956,27 +29952,27 @@
         <v>41</v>
       </c>
       <c r="H386">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I386" s="2">
         <f t="shared" ref="I386:I449" si="12">H386*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J386" s="2">
         <f t="shared" ref="J386:J449" si="13">H386*1.75</f>
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="L386">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M386">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N386">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O386">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P386">
         <v>0</v>
@@ -30026,27 +30022,27 @@
         <v>36</v>
       </c>
       <c r="H387">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I387" s="2">
         <f t="shared" si="12"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J387" s="2">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K387" t="s">
         <v>265</v>
       </c>
       <c r="L387">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M387">
-        <v>5.58</v>
+        <v>5.57</v>
       </c>
       <c r="N387">
-        <v>5.58</v>
+        <v>5.57</v>
       </c>
       <c r="O387">
         <v>0</v>
@@ -30113,13 +30109,13 @@
         <v>234</v>
       </c>
       <c r="L388">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M388">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="N388">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="O388">
         <v>0</v>
@@ -30172,30 +30168,30 @@
         <v>34</v>
       </c>
       <c r="H389">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I389" s="2">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J389" s="2">
         <f t="shared" si="13"/>
-        <v>26.25</v>
+        <v>29.75</v>
       </c>
       <c r="K389" t="s">
         <v>180</v>
       </c>
       <c r="L389">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M389">
-        <v>6.38</v>
+        <v>6.39</v>
       </c>
       <c r="N389">
-        <v>6.69</v>
+        <v>7</v>
       </c>
       <c r="O389">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P389">
         <v>0</v>
@@ -30245,30 +30241,30 @@
         <v>100</v>
       </c>
       <c r="H390">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I390" s="2">
         <f t="shared" si="12"/>
-        <v>5.2</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="J390" s="2">
         <f t="shared" si="13"/>
-        <v>45.5</v>
+        <v>49</v>
       </c>
       <c r="K390" t="s">
         <v>95</v>
       </c>
       <c r="L390">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M390">
-        <v>6.36</v>
+        <v>6.5</v>
       </c>
       <c r="N390">
-        <v>7.43</v>
+        <v>7.94</v>
       </c>
       <c r="O390">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P390">
         <v>0</v>
@@ -30286,7 +30282,7 @@
         <v>0</v>
       </c>
       <c r="U390">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V390">
         <v>1</v>
@@ -30531,24 +30527,24 @@
         <v>34</v>
       </c>
       <c r="H394">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I394" s="2">
         <f t="shared" si="12"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J394" s="2">
         <f t="shared" si="13"/>
+        <v>5.25</v>
+      </c>
+      <c r="L394">
         <v>7</v>
-      </c>
-      <c r="L394">
-        <v>6</v>
       </c>
       <c r="M394">
         <v>5.5</v>
       </c>
       <c r="N394">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="O394">
         <v>0</v>
@@ -30578,7 +30574,7 @@
         <v>0</v>
       </c>
       <c r="X394">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395" spans="1:24" x14ac:dyDescent="0.2">
@@ -30601,15 +30597,15 @@
         <v>34</v>
       </c>
       <c r="H395">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I395" s="2">
         <f t="shared" si="12"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="J395" s="2">
         <f t="shared" si="13"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="L395">
         <v>6</v>
@@ -30671,27 +30667,27 @@
         <v>34</v>
       </c>
       <c r="H396">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I396" s="2">
         <f t="shared" si="12"/>
-        <v>1.4000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J396" s="2">
         <f t="shared" si="13"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="K396" t="s">
         <v>27</v>
       </c>
       <c r="L396">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M396">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="N396">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="O396">
         <v>0</v>
@@ -30898,13 +30894,13 @@
         <v>156</v>
       </c>
       <c r="L399">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M399">
-        <v>5.69</v>
+        <v>5.78</v>
       </c>
       <c r="N399">
-        <v>5.62</v>
+        <v>5.72</v>
       </c>
       <c r="O399">
         <v>0</v>
@@ -31038,13 +31034,13 @@
         <v>15.75</v>
       </c>
       <c r="L401">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M401">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="N401">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="O401">
         <v>1</v>
@@ -31097,15 +31093,15 @@
         <v>45</v>
       </c>
       <c r="H402">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I402" s="2">
         <f t="shared" si="12"/>
-        <v>2.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J402" s="2">
         <f t="shared" si="13"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="K402" t="s">
         <v>30</v>
@@ -31313,27 +31309,27 @@
         <v>34</v>
       </c>
       <c r="H405">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I405" s="2">
         <f t="shared" si="12"/>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J405" s="2">
         <f t="shared" si="13"/>
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="K405" t="s">
         <v>127</v>
       </c>
       <c r="L405">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M405">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="N405">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="O405">
         <v>0</v>
@@ -31386,15 +31382,15 @@
         <v>34</v>
       </c>
       <c r="H406">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I406" s="2">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J406" s="2">
         <f t="shared" si="13"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="K406" t="s">
         <v>95</v>
@@ -31459,15 +31455,15 @@
         <v>26</v>
       </c>
       <c r="H407">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I407" s="2">
         <f t="shared" si="12"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J407" s="2">
         <f t="shared" si="13"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K407" t="s">
         <v>156</v>
@@ -31885,24 +31881,24 @@
         <v>29</v>
       </c>
       <c r="H413">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I413" s="2">
         <f t="shared" si="12"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J413" s="2">
         <f t="shared" si="13"/>
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="L413">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M413">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="N413">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O413">
         <v>0</v>
@@ -31969,13 +31965,13 @@
         <v>234</v>
       </c>
       <c r="L414">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M414">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="N414">
-        <v>5.62</v>
+        <v>5.5</v>
       </c>
       <c r="O414">
         <v>0</v>
@@ -32042,13 +32038,13 @@
         <v>27</v>
       </c>
       <c r="L415">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M415">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="N415">
-        <v>6.86</v>
+        <v>6.56</v>
       </c>
       <c r="O415">
         <v>2</v>
@@ -32072,7 +32068,7 @@
         <v>0</v>
       </c>
       <c r="V415">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W415">
         <v>0</v>
@@ -32101,24 +32097,24 @@
         <v>39</v>
       </c>
       <c r="H416">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I416" s="2">
         <f t="shared" si="12"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J416" s="2">
         <f t="shared" si="13"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
       <c r="L416">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M416">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="N416">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="O416">
         <v>0</v>
@@ -32171,24 +32167,24 @@
         <v>45</v>
       </c>
       <c r="H417">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I417" s="2">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J417" s="2">
         <f t="shared" si="13"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="L417">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M417">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="N417">
-        <v>5.69</v>
+        <v>5.78</v>
       </c>
       <c r="O417">
         <v>0</v>
@@ -32252,13 +32248,13 @@
         <v>15.75</v>
       </c>
       <c r="L418">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M418">
-        <v>6.07</v>
+        <v>5.94</v>
       </c>
       <c r="N418">
-        <v>6.43</v>
+        <v>6.25</v>
       </c>
       <c r="O418">
         <v>1</v>
@@ -32538,13 +32534,13 @@
         <v>156</v>
       </c>
       <c r="L422">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M422">
-        <v>6.38</v>
+        <v>6.28</v>
       </c>
       <c r="N422">
-        <v>8.25</v>
+        <v>7.94</v>
       </c>
       <c r="O422">
         <v>5</v>
@@ -32597,27 +32593,27 @@
         <v>33</v>
       </c>
       <c r="H423">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I423" s="2">
         <f t="shared" si="12"/>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="J423" s="2">
         <f t="shared" si="13"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K423" t="s">
         <v>27</v>
       </c>
       <c r="L423">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M423">
-        <v>5.62</v>
+        <v>5.56</v>
       </c>
       <c r="N423">
-        <v>6.31</v>
+        <v>6.11</v>
       </c>
       <c r="O423">
         <v>2</v>
@@ -32641,7 +32637,7 @@
         <v>0</v>
       </c>
       <c r="V423">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W423">
         <v>0</v>
@@ -32754,13 +32750,13 @@
         <v>156</v>
       </c>
       <c r="L425">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M425">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="N425">
-        <v>6.36</v>
+        <v>6.25</v>
       </c>
       <c r="O425">
         <v>0</v>
@@ -32897,13 +32893,13 @@
         <v>27</v>
       </c>
       <c r="L427">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M427">
         <v>6</v>
       </c>
       <c r="N427">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="O427">
         <v>0</v>
@@ -32956,24 +32952,24 @@
         <v>34</v>
       </c>
       <c r="H428">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I428" s="2">
         <f t="shared" si="12"/>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J428" s="2">
         <f t="shared" si="13"/>
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="L428">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M428">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N428">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O428">
         <v>0</v>
@@ -33099,27 +33095,27 @@
         <v>62</v>
       </c>
       <c r="H430">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I430" s="2">
         <f t="shared" si="12"/>
-        <v>2.4000000000000004</v>
+        <v>2.6</v>
       </c>
       <c r="J430" s="2">
         <f t="shared" si="13"/>
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="K430" t="s">
         <v>30</v>
       </c>
       <c r="L430">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M430">
-        <v>6.21</v>
+        <v>6.19</v>
       </c>
       <c r="N430">
-        <v>6.64</v>
+        <v>6.56</v>
       </c>
       <c r="O430">
         <v>1</v>
@@ -33172,27 +33168,27 @@
         <v>33</v>
       </c>
       <c r="H431">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I431" s="2">
         <f t="shared" si="12"/>
-        <v>3.8000000000000003</v>
+        <v>4</v>
       </c>
       <c r="J431" s="2">
         <f t="shared" si="13"/>
-        <v>33.25</v>
+        <v>35</v>
       </c>
       <c r="K431" t="s">
         <v>95</v>
       </c>
       <c r="L431">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M431">
-        <v>6.43</v>
+        <v>6.38</v>
       </c>
       <c r="N431">
-        <v>7.36</v>
+        <v>7.19</v>
       </c>
       <c r="O431">
         <v>2</v>
@@ -33245,27 +33241,27 @@
         <v>36</v>
       </c>
       <c r="H432">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I432" s="2">
         <f t="shared" si="12"/>
-        <v>3.2</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J432" s="2">
         <f t="shared" si="13"/>
-        <v>28</v>
+        <v>29.75</v>
       </c>
       <c r="K432" t="s">
         <v>156</v>
       </c>
       <c r="L432">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M432">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="N432">
-        <v>7.12</v>
+        <v>7.06</v>
       </c>
       <c r="O432">
         <v>3</v>
@@ -33388,24 +33384,24 @@
         <v>60</v>
       </c>
       <c r="H434">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I434" s="2">
         <f t="shared" si="12"/>
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J434" s="2">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="L434">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M434">
-        <v>6</v>
+        <v>6.14</v>
       </c>
       <c r="N434">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="O434">
         <v>1</v>
@@ -33426,7 +33422,7 @@
         <v>0</v>
       </c>
       <c r="U434">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V434">
         <v>0</v>
@@ -33528,30 +33524,30 @@
         <v>91</v>
       </c>
       <c r="H436">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I436" s="2">
         <f t="shared" si="12"/>
-        <v>3.8000000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="J436" s="2">
         <f t="shared" si="13"/>
-        <v>33.25</v>
+        <v>36.75</v>
       </c>
       <c r="K436" t="s">
         <v>30</v>
       </c>
       <c r="L436">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M436">
-        <v>6.07</v>
+        <v>6.19</v>
       </c>
       <c r="N436">
-        <v>6.79</v>
+        <v>7.19</v>
       </c>
       <c r="O436">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P436">
         <v>0</v>
@@ -33615,13 +33611,13 @@
         <v>234</v>
       </c>
       <c r="L437">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M437">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="N437">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="O437">
         <v>0</v>
@@ -33817,27 +33813,27 @@
         <v>39</v>
       </c>
       <c r="H440">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I440" s="2">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J440" s="2">
         <f t="shared" si="13"/>
-        <v>8.75</v>
+        <v>12.25</v>
       </c>
       <c r="L440">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M440">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="N440">
-        <v>5.81</v>
+        <v>6.28</v>
       </c>
       <c r="O440">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P440">
         <v>0</v>
@@ -33957,15 +33953,15 @@
         <v>619</v>
       </c>
       <c r="H442">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I442" s="2">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J442" s="2">
         <f t="shared" si="13"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L442">
         <v>0</v>
@@ -34027,24 +34023,24 @@
         <v>34</v>
       </c>
       <c r="H443">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I443" s="2">
         <f t="shared" si="12"/>
-        <v>1.2000000000000002</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J443" s="2">
         <f t="shared" si="13"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="L443">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M443">
-        <v>6.33</v>
+        <v>5.75</v>
       </c>
       <c r="N443">
-        <v>8.33</v>
+        <v>7.25</v>
       </c>
       <c r="O443">
         <v>2</v>
@@ -34377,15 +34373,15 @@
         <v>60</v>
       </c>
       <c r="H448">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I448" s="2">
         <f t="shared" si="12"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J448" s="2">
         <f t="shared" si="13"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="L448">
         <v>3</v>
@@ -34657,30 +34653,30 @@
         <v>39</v>
       </c>
       <c r="H452">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I452" s="2">
         <f t="shared" si="14"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J452" s="2">
         <f t="shared" si="15"/>
-        <v>1.75</v>
+        <v>8.75</v>
       </c>
       <c r="K452" t="s">
         <v>265</v>
       </c>
       <c r="L452">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M452">
-        <v>5.25</v>
+        <v>5.83</v>
       </c>
       <c r="N452">
-        <v>5.25</v>
+        <v>6.83</v>
       </c>
       <c r="O452">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P452">
         <v>0</v>
@@ -34730,27 +34726,27 @@
         <v>35</v>
       </c>
       <c r="H453">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I453" s="2">
         <f t="shared" si="14"/>
-        <v>3.6</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J453" s="2">
         <f t="shared" si="15"/>
-        <v>31.5</v>
+        <v>29.75</v>
       </c>
       <c r="K453" t="s">
         <v>127</v>
       </c>
       <c r="L453">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M453">
-        <v>6.42</v>
+        <v>6.36</v>
       </c>
       <c r="N453">
-        <v>6.75</v>
+        <v>6.64</v>
       </c>
       <c r="O453">
         <v>0</v>
@@ -34814,13 +34810,13 @@
         <v>3.5</v>
       </c>
       <c r="L454">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M454">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="N454">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="O454">
         <v>0</v>
@@ -34954,13 +34950,13 @@
         <v>14</v>
       </c>
       <c r="L456">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M456">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="N456">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="O456">
         <v>1</v>
@@ -35094,13 +35090,13 @@
         <v>10.5</v>
       </c>
       <c r="L458">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M458">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="N458">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="O458">
         <v>0</v>
@@ -35363,24 +35359,24 @@
         <v>29</v>
       </c>
       <c r="H462">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I462" s="2">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J462" s="2">
         <f t="shared" si="15"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K462" t="s">
         <v>27</v>
       </c>
       <c r="L462">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M462">
-        <v>5.67</v>
+        <v>5.71</v>
       </c>
       <c r="N462">
         <v>5.5</v>
@@ -35407,7 +35403,7 @@
         <v>0</v>
       </c>
       <c r="V462">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W462">
         <v>0</v>
@@ -35447,13 +35443,13 @@
         <v>7</v>
       </c>
       <c r="L463">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M463">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="N463">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="O463">
         <v>0</v>
@@ -35520,7 +35516,7 @@
         <v>180</v>
       </c>
       <c r="L464">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M464">
         <v>5.5</v>
@@ -35579,27 +35575,27 @@
         <v>39</v>
       </c>
       <c r="H465">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I465" s="2">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J465" s="2">
         <f t="shared" si="15"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="K465" t="s">
         <v>234</v>
       </c>
       <c r="L465">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M465">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="N465">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="O465">
         <v>1</v>
@@ -35623,7 +35619,7 @@
         <v>3</v>
       </c>
       <c r="V465">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W465">
         <v>0</v>
@@ -35652,27 +35648,27 @@
         <v>36</v>
       </c>
       <c r="H466">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I466" s="2">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J466" s="2">
         <f t="shared" si="15"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="K466" t="s">
         <v>30</v>
       </c>
       <c r="L466">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M466">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="N466">
-        <v>7.12</v>
+        <v>6.9</v>
       </c>
       <c r="O466">
         <v>1</v>
@@ -35725,15 +35721,15 @@
         <v>100</v>
       </c>
       <c r="H467">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I467" s="2">
         <f t="shared" si="14"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J467" s="2">
         <f t="shared" si="15"/>
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="L467">
         <v>1</v>
@@ -35795,27 +35791,27 @@
         <v>34</v>
       </c>
       <c r="H468">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I468" s="2">
         <f t="shared" si="14"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J468" s="2">
         <f t="shared" si="15"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="K468" t="s">
         <v>265</v>
       </c>
       <c r="L468">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M468">
-        <v>5.56</v>
+        <v>5.78</v>
       </c>
       <c r="N468">
-        <v>5.38</v>
+        <v>5.61</v>
       </c>
       <c r="O468">
         <v>0</v>
@@ -35952,13 +35948,13 @@
         <v>12.25</v>
       </c>
       <c r="L470">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M470">
-        <v>5.75</v>
+        <v>5.61</v>
       </c>
       <c r="N470">
-        <v>6.06</v>
+        <v>5.83</v>
       </c>
       <c r="O470">
         <v>1</v>
@@ -35982,7 +35978,7 @@
         <v>0</v>
       </c>
       <c r="V470">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W470">
         <v>0</v>
@@ -36011,24 +36007,24 @@
         <v>47</v>
       </c>
       <c r="H471">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I471" s="2">
         <f t="shared" si="14"/>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J471" s="2">
         <f t="shared" si="15"/>
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="L471">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M471">
         <v>6</v>
       </c>
       <c r="N471">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="O471">
         <v>1</v>
@@ -36049,7 +36045,7 @@
         <v>0</v>
       </c>
       <c r="U471">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V471">
         <v>0</v>
@@ -36162,13 +36158,13 @@
         <v>7</v>
       </c>
       <c r="L473">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M473">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="N473">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="O473">
         <v>0</v>
@@ -36305,13 +36301,13 @@
         <v>95</v>
       </c>
       <c r="L475">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M475">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="N475">
-        <v>5.62</v>
+        <v>5.6</v>
       </c>
       <c r="O475">
         <v>0</v>
@@ -36437,27 +36433,27 @@
         <v>29</v>
       </c>
       <c r="H477">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I477" s="2">
         <f t="shared" si="14"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J477" s="2">
         <f t="shared" si="15"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="K477" t="s">
         <v>265</v>
       </c>
       <c r="L477">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M477">
-        <v>5.75</v>
+        <v>5.72</v>
       </c>
       <c r="N477">
-        <v>5.69</v>
+        <v>5.61</v>
       </c>
       <c r="O477">
         <v>0</v>
@@ -36481,7 +36477,7 @@
         <v>0</v>
       </c>
       <c r="V477">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W477">
         <v>0</v>
@@ -36591,13 +36587,13 @@
         <v>14</v>
       </c>
       <c r="L479">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M479">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="N479">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="O479">
         <v>0</v>
@@ -36807,19 +36803,19 @@
         <v>156</v>
       </c>
       <c r="L482">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M482">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="N482">
-        <v>4.62</v>
+        <v>4.2</v>
       </c>
       <c r="O482">
         <v>0</v>
       </c>
       <c r="P482">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q482">
         <v>0</v>
@@ -36880,13 +36876,13 @@
         <v>156</v>
       </c>
       <c r="L483">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M483">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="N483">
-        <v>6.62</v>
+        <v>6.5</v>
       </c>
       <c r="O483">
         <v>1</v>
@@ -37079,30 +37075,30 @@
         <v>45</v>
       </c>
       <c r="H486">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I486" s="2">
         <f t="shared" si="14"/>
-        <v>2.8000000000000003</v>
+        <v>3.2</v>
       </c>
       <c r="J486" s="2">
         <f t="shared" si="15"/>
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="K486" t="s">
         <v>180</v>
       </c>
       <c r="L486">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M486">
-        <v>6.31</v>
+        <v>6.44</v>
       </c>
       <c r="N486">
-        <v>6.62</v>
+        <v>7.11</v>
       </c>
       <c r="O486">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P486">
         <v>0</v>
@@ -37120,10 +37116,10 @@
         <v>0</v>
       </c>
       <c r="U486">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V486">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W486">
         <v>0</v>
@@ -37233,13 +37229,13 @@
         <v>3.5</v>
       </c>
       <c r="L488">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M488">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N488">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O488">
         <v>0</v>
@@ -37373,13 +37369,13 @@
         <v>7</v>
       </c>
       <c r="L490">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M490">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="N490">
-        <v>5.5</v>
+        <v>5.39</v>
       </c>
       <c r="O490">
         <v>0</v>
@@ -37403,7 +37399,7 @@
         <v>0</v>
       </c>
       <c r="V490">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W490">
         <v>0</v>
@@ -37432,15 +37428,15 @@
         <v>78</v>
       </c>
       <c r="H491">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I491" s="2">
         <f t="shared" si="14"/>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J491" s="2">
         <f t="shared" si="15"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="L491">
         <v>5</v>
@@ -37502,15 +37498,15 @@
         <v>42</v>
       </c>
       <c r="H492">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I492" s="2">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J492" s="2">
         <f t="shared" si="15"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L492">
         <v>3</v>
@@ -37572,24 +37568,24 @@
         <v>26</v>
       </c>
       <c r="H493">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I493" s="2">
         <f t="shared" si="14"/>
-        <v>1.4000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J493" s="2">
         <f t="shared" si="15"/>
-        <v>12.25</v>
+        <v>15.75</v>
       </c>
       <c r="L493">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M493">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="N493">
-        <v>4.38</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="O493">
         <v>0</v>
@@ -37785,24 +37781,24 @@
         <v>47</v>
       </c>
       <c r="H496">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I496" s="2">
         <f t="shared" si="14"/>
-        <v>0.60000000000000009</v>
+        <v>1</v>
       </c>
       <c r="J496" s="2">
         <f t="shared" si="15"/>
-        <v>5.25</v>
+        <v>8.75</v>
       </c>
       <c r="L496">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M496">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="N496">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="O496">
         <v>0</v>
@@ -38079,13 +38075,13 @@
         <v>21</v>
       </c>
       <c r="L500">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M500">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
       <c r="N500">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="O500">
         <v>1</v>
@@ -38138,24 +38134,24 @@
         <v>33</v>
       </c>
       <c r="H501">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I501" s="2">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J501" s="2">
         <f t="shared" si="15"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="L501">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M501">
-        <v>6.2</v>
+        <v>6.08</v>
       </c>
       <c r="N501">
-        <v>7.4</v>
+        <v>7.08</v>
       </c>
       <c r="O501">
         <v>2</v>
@@ -38208,15 +38204,15 @@
         <v>41</v>
       </c>
       <c r="H502">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I502" s="2">
         <f t="shared" si="14"/>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J502" s="2">
         <f t="shared" si="15"/>
-        <v>19.25</v>
+        <v>17.5</v>
       </c>
       <c r="K502" t="s">
         <v>234</v>
@@ -38494,24 +38490,24 @@
         <v>33</v>
       </c>
       <c r="H506">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I506" s="2">
         <f t="shared" si="14"/>
-        <v>2.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J506" s="2">
         <f t="shared" si="15"/>
-        <v>19.25</v>
+        <v>21</v>
       </c>
       <c r="L506">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M506">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="N506">
-        <v>6.69</v>
+        <v>6.61</v>
       </c>
       <c r="O506">
         <v>1</v>
@@ -38844,24 +38840,24 @@
         <v>36</v>
       </c>
       <c r="H511">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I511" s="2">
         <f t="shared" si="14"/>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J511" s="2">
         <f t="shared" si="15"/>
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="L511">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M511">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="N511">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="O511">
         <v>0</v>
@@ -38928,13 +38924,13 @@
         <v>180</v>
       </c>
       <c r="L512">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M512">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="N512">
-        <v>5.21</v>
+        <v>5.31</v>
       </c>
       <c r="O512">
         <v>0</v>
@@ -38958,7 +38954,7 @@
         <v>0</v>
       </c>
       <c r="V512">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W512">
         <v>0</v>
@@ -38987,24 +38983,24 @@
         <v>26</v>
       </c>
       <c r="H513">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I513" s="2">
         <f t="shared" si="14"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J513" s="2">
         <f t="shared" si="15"/>
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="L513">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M513">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N513">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O513">
         <v>0</v>
@@ -39057,27 +39053,27 @@
         <v>47</v>
       </c>
       <c r="H514">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I514" s="2">
         <f t="shared" ref="I514:I577" si="16">H514*0.2</f>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J514" s="2">
         <f t="shared" ref="J514:J577" si="17">H514*1.75</f>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="K514" t="s">
         <v>156</v>
       </c>
       <c r="L514">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M514">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
       <c r="N514">
-        <v>6.3</v>
+        <v>6.33</v>
       </c>
       <c r="O514">
         <v>0</v>
@@ -39130,15 +39126,15 @@
         <v>42</v>
       </c>
       <c r="H515">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I515" s="2">
         <f t="shared" si="16"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J515" s="2">
         <f t="shared" si="17"/>
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="K515" t="s">
         <v>156</v>
@@ -39203,27 +39199,27 @@
         <v>42</v>
       </c>
       <c r="H516">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I516" s="2">
         <f t="shared" si="16"/>
-        <v>2.6</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J516" s="2">
         <f t="shared" si="17"/>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="K516" t="s">
         <v>234</v>
       </c>
       <c r="L516">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M516">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
       <c r="N516">
-        <v>7.2</v>
+        <v>7.08</v>
       </c>
       <c r="O516">
         <v>1</v>
@@ -39287,13 +39283,13 @@
         <v>5.25</v>
       </c>
       <c r="L517">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M517">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="N517">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="O517">
         <v>0</v>
@@ -39360,13 +39356,13 @@
         <v>180</v>
       </c>
       <c r="L518">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M518">
         <v>6</v>
       </c>
       <c r="N518">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="O518">
         <v>0</v>
@@ -39419,15 +39415,15 @@
         <v>33</v>
       </c>
       <c r="H519">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I519" s="2">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J519" s="2">
         <f t="shared" si="17"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K519" t="s">
         <v>156</v>
@@ -39842,27 +39838,27 @@
         <v>47</v>
       </c>
       <c r="H525">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I525" s="2">
         <f t="shared" si="16"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J525" s="2">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="K525" t="s">
         <v>30</v>
       </c>
       <c r="L525">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M525">
-        <v>5.62</v>
+        <v>5.7</v>
       </c>
       <c r="N525">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O525">
         <v>0</v>
@@ -39996,13 +39992,13 @@
         <v>14</v>
       </c>
       <c r="L527">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M527">
-        <v>6.21</v>
+        <v>6.19</v>
       </c>
       <c r="N527">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="O527">
         <v>0</v>
@@ -40335,27 +40331,27 @@
         <v>47</v>
       </c>
       <c r="H532">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I532" s="2">
         <f t="shared" si="16"/>
-        <v>3.4000000000000004</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J532" s="2">
         <f t="shared" si="17"/>
-        <v>29.75</v>
+        <v>33.25</v>
       </c>
       <c r="L532">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M532">
-        <v>6.69</v>
+        <v>6.78</v>
       </c>
       <c r="N532">
-        <v>8.06</v>
+        <v>8.33</v>
       </c>
       <c r="O532">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P532">
         <v>0</v>
@@ -40364,10 +40360,10 @@
         <v>0</v>
       </c>
       <c r="R532">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S532">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T532">
         <v>0</v>
@@ -40405,27 +40401,27 @@
         <v>47</v>
       </c>
       <c r="H533">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I533" s="2">
         <f t="shared" si="16"/>
-        <v>0.8</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J533" s="2">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>12.25</v>
       </c>
       <c r="L533">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M533">
-        <v>5.83</v>
+        <v>6.12</v>
       </c>
       <c r="N533">
-        <v>5.83</v>
+        <v>6.88</v>
       </c>
       <c r="O533">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P533">
         <v>0</v>
@@ -40626,13 +40622,13 @@
         <v>5.25</v>
       </c>
       <c r="L536">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M536">
-        <v>5.88</v>
+        <v>5.8</v>
       </c>
       <c r="N536">
-        <v>5.88</v>
+        <v>5.8</v>
       </c>
       <c r="O536">
         <v>0</v>
@@ -40696,7 +40692,7 @@
         <v>1.75</v>
       </c>
       <c r="L537">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M537">
         <v>5.5</v>
@@ -40726,7 +40722,7 @@
         <v>0</v>
       </c>
       <c r="V537">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W537">
         <v>0</v>
@@ -40906,13 +40902,13 @@
         <v>3.5</v>
       </c>
       <c r="L540">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M540">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="N540">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O540">
         <v>0</v>
@@ -40976,13 +40972,13 @@
         <v>3.5</v>
       </c>
       <c r="L541">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M541">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="N541">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="O541">
         <v>0</v>
@@ -41035,24 +41031,24 @@
         <v>33</v>
       </c>
       <c r="H542">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I542" s="2">
         <f t="shared" si="16"/>
-        <v>2.6</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J542" s="2">
         <f t="shared" si="17"/>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="K542" t="s">
         <v>156</v>
       </c>
       <c r="L542">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M542">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="N542">
         <v>6.5</v>
@@ -41108,27 +41104,27 @@
         <v>42</v>
       </c>
       <c r="H543">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I543" s="2">
         <f t="shared" si="16"/>
-        <v>2.6</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J543" s="2">
         <f t="shared" si="17"/>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="K543" t="s">
         <v>156</v>
       </c>
       <c r="L543">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M543">
-        <v>6.25</v>
+        <v>6.11</v>
       </c>
       <c r="N543">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -41181,27 +41177,27 @@
         <v>33</v>
       </c>
       <c r="H544">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I544" s="2">
         <f t="shared" si="16"/>
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J544" s="2">
         <f t="shared" si="17"/>
-        <v>28</v>
+        <v>31.5</v>
       </c>
       <c r="L544">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M544">
         <v>7</v>
       </c>
       <c r="N544">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
       <c r="O544">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P544">
         <v>0</v>
@@ -41262,13 +41258,13 @@
         <v>3.5</v>
       </c>
       <c r="L545">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M545">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N545">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O545">
         <v>0</v>
@@ -41475,7 +41471,7 @@
         <v>8.75</v>
       </c>
       <c r="L548">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M548">
         <v>6</v>
@@ -41604,15 +41600,15 @@
         <v>34</v>
       </c>
       <c r="H550">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I550" s="2">
         <f t="shared" si="16"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J550" s="2">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="L550">
         <v>2</v>
@@ -41814,27 +41810,27 @@
         <v>47</v>
       </c>
       <c r="H553">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I553" s="2">
         <f t="shared" si="16"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J553" s="2">
         <f t="shared" si="17"/>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
       <c r="K553" t="s">
         <v>180</v>
       </c>
       <c r="L553">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M553">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="N553">
-        <v>6.67</v>
+        <v>6.79</v>
       </c>
       <c r="O553">
         <v>1</v>
@@ -41855,7 +41851,7 @@
         <v>0</v>
       </c>
       <c r="U553">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V553">
         <v>0</v>
@@ -41960,18 +41956,18 @@
         <v>42</v>
       </c>
       <c r="H555">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I555" s="2">
         <f t="shared" si="16"/>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J555" s="2">
         <f t="shared" si="17"/>
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="L555">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M555">
         <v>6</v>
@@ -42030,24 +42026,24 @@
         <v>34</v>
       </c>
       <c r="H556">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I556" s="2">
         <f t="shared" si="16"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J556" s="2">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="L556">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M556">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="N556">
-        <v>4.9000000000000004</v>
+        <v>4.75</v>
       </c>
       <c r="O556">
         <v>0</v>
@@ -42077,7 +42073,7 @@
         <v>0</v>
       </c>
       <c r="X556">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557" spans="1:24" x14ac:dyDescent="0.2">
@@ -42240,24 +42236,24 @@
         <v>60</v>
       </c>
       <c r="H559">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I559" s="2">
         <f t="shared" si="16"/>
-        <v>2.2000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J559" s="2">
         <f t="shared" si="17"/>
-        <v>19.25</v>
+        <v>21</v>
       </c>
       <c r="L559">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M559">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="N559">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="O559">
         <v>2</v>
@@ -42278,7 +42274,7 @@
         <v>0</v>
       </c>
       <c r="U559">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V559">
         <v>0</v>
@@ -42310,15 +42306,15 @@
         <v>33</v>
       </c>
       <c r="H560">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I560" s="2">
         <f t="shared" si="16"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J560" s="2">
         <f t="shared" si="17"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="L560">
         <v>4</v>
@@ -42520,24 +42516,24 @@
         <v>36</v>
       </c>
       <c r="H563">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I563" s="2">
         <f t="shared" si="16"/>
-        <v>3.2</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J563" s="2">
         <f t="shared" si="17"/>
-        <v>28</v>
+        <v>29.75</v>
       </c>
       <c r="L563">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M563">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="N563">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="O563">
         <v>2</v>
@@ -42558,7 +42554,7 @@
         <v>0</v>
       </c>
       <c r="U563">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V563">
         <v>2</v>
@@ -42601,13 +42597,13 @@
         <v>3.5</v>
       </c>
       <c r="L564">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M564">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="N564">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O564">
         <v>0</v>
@@ -42660,27 +42656,27 @@
         <v>33</v>
       </c>
       <c r="H565">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I565" s="2">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J565" s="2">
         <f t="shared" si="17"/>
-        <v>26.25</v>
+        <v>28</v>
       </c>
       <c r="K565" t="s">
         <v>127</v>
       </c>
       <c r="L565">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M565">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="N565">
-        <v>7.14</v>
+        <v>6.94</v>
       </c>
       <c r="O565">
         <v>2</v>
@@ -42733,30 +42729,30 @@
         <v>91</v>
       </c>
       <c r="H566">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I566" s="2">
         <f t="shared" si="16"/>
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J566" s="2">
         <f t="shared" si="17"/>
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="K566" t="s">
         <v>180</v>
       </c>
       <c r="L566">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M566">
-        <v>6.25</v>
+        <v>6.43</v>
       </c>
       <c r="N566">
-        <v>6.75</v>
+        <v>7.29</v>
       </c>
       <c r="O566">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P566">
         <v>0</v>
@@ -42960,13 +42956,13 @@
         <v>27</v>
       </c>
       <c r="L569">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M569">
-        <v>6.06</v>
+        <v>6</v>
       </c>
       <c r="N569">
-        <v>6.81</v>
+        <v>6.61</v>
       </c>
       <c r="O569">
         <v>2</v>
@@ -42990,7 +42986,7 @@
         <v>0</v>
       </c>
       <c r="V569">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W569">
         <v>0</v>
@@ -43372,24 +43368,24 @@
         <v>39</v>
       </c>
       <c r="H575">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I575" s="2">
         <f t="shared" si="16"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J575" s="2">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="L575">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M575">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="N575">
-        <v>6.1</v>
+        <v>6.08</v>
       </c>
       <c r="O575">
         <v>0</v>
@@ -43410,7 +43406,7 @@
         <v>0</v>
       </c>
       <c r="U575">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V575">
         <v>0</v>
@@ -43442,24 +43438,24 @@
         <v>62</v>
       </c>
       <c r="H576">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I576" s="2">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J576" s="2">
         <f t="shared" si="17"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="L576">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M576">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="N576">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="O576">
         <v>0</v>
@@ -43483,7 +43479,7 @@
         <v>1</v>
       </c>
       <c r="V576">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W576">
         <v>0</v>
@@ -43652,24 +43648,24 @@
         <v>34</v>
       </c>
       <c r="H579">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I579" s="2">
         <f t="shared" si="18"/>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J579" s="2">
         <f t="shared" si="19"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="L579">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M579">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="N579">
-        <v>6.1</v>
+        <v>5.67</v>
       </c>
       <c r="O579">
         <v>0</v>
@@ -43699,7 +43695,7 @@
         <v>0</v>
       </c>
       <c r="X579">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="580" spans="1:24" x14ac:dyDescent="0.2">
@@ -43722,30 +43718,30 @@
         <v>35</v>
       </c>
       <c r="H580">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I580" s="2">
         <f t="shared" si="18"/>
-        <v>1.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="J580" s="2">
         <f t="shared" si="19"/>
-        <v>10.5</v>
+        <v>15.75</v>
       </c>
       <c r="K580" t="s">
         <v>127</v>
       </c>
       <c r="L580">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M580">
-        <v>6.4</v>
+        <v>6.58</v>
       </c>
       <c r="N580">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="O580">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P580">
         <v>0</v>
@@ -43763,7 +43759,7 @@
         <v>0</v>
       </c>
       <c r="U580">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V580">
         <v>0</v>
@@ -43795,24 +43791,24 @@
         <v>33</v>
       </c>
       <c r="H581">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I581" s="2">
         <f t="shared" si="18"/>
-        <v>2.4000000000000004</v>
+        <v>2.6</v>
       </c>
       <c r="J581" s="2">
         <f t="shared" si="19"/>
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="L581">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M581">
-        <v>6.14</v>
+        <v>6.19</v>
       </c>
       <c r="N581">
-        <v>7.57</v>
+        <v>7.44</v>
       </c>
       <c r="O581">
         <v>3</v>
@@ -43876,13 +43872,13 @@
         <v>15.75</v>
       </c>
       <c r="L582">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M582">
-        <v>5.86</v>
+        <v>5.81</v>
       </c>
       <c r="N582">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="O582">
         <v>1</v>
@@ -44145,15 +44141,15 @@
         <v>45</v>
       </c>
       <c r="H586">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I586" s="2">
         <f t="shared" si="18"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="J586" s="2">
         <f t="shared" si="19"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="L586">
         <v>3</v>
@@ -44215,27 +44211,27 @@
         <v>33</v>
       </c>
       <c r="H587">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I587" s="2">
         <f t="shared" si="18"/>
-        <v>0.60000000000000009</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J587" s="2">
         <f t="shared" si="19"/>
-        <v>5.25</v>
+        <v>12.25</v>
       </c>
       <c r="L587">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M587">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N587">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="O587">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P587">
         <v>0</v>
@@ -44355,15 +44351,15 @@
         <v>33</v>
       </c>
       <c r="H589">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I589" s="2">
         <f t="shared" si="18"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J589" s="2">
         <f t="shared" si="19"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="L589">
         <v>2</v>
@@ -44436,13 +44432,13 @@
         <v>3.5</v>
       </c>
       <c r="L590">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M590">
-        <v>5.62</v>
+        <v>5.7</v>
       </c>
       <c r="N590">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O590">
         <v>0</v>
@@ -44495,24 +44491,24 @@
         <v>41</v>
       </c>
       <c r="H591">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I591" s="2">
         <f t="shared" si="18"/>
-        <v>1.4000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J591" s="2">
         <f t="shared" si="19"/>
-        <v>12.25</v>
+        <v>15.75</v>
       </c>
       <c r="L591">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M591">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="N591">
-        <v>7.5</v>
+        <v>7.17</v>
       </c>
       <c r="O591">
         <v>1</v>
@@ -44565,27 +44561,27 @@
         <v>41</v>
       </c>
       <c r="H592">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I592" s="2">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J592" s="2">
         <f t="shared" si="19"/>
-        <v>8.75</v>
+        <v>12.25</v>
       </c>
       <c r="L592">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M592">
-        <v>5.38</v>
+        <v>5.6</v>
       </c>
       <c r="N592">
-        <v>5.38</v>
+        <v>6.2</v>
       </c>
       <c r="O592">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P592">
         <v>0</v>
@@ -44635,24 +44631,24 @@
         <v>60</v>
       </c>
       <c r="H593">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I593" s="2">
         <f t="shared" si="18"/>
-        <v>1.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J593" s="2">
         <f t="shared" si="19"/>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="L593">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M593">
         <v>6</v>
       </c>
       <c r="N593">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O593">
         <v>1</v>
@@ -44716,13 +44712,13 @@
         <v>10.5</v>
       </c>
       <c r="L594">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M594">
-        <v>5.8</v>
+        <v>5.58</v>
       </c>
       <c r="N594">
-        <v>5.8</v>
+        <v>5.58</v>
       </c>
       <c r="O594">
         <v>0</v>
@@ -44845,24 +44841,24 @@
         <v>41</v>
       </c>
       <c r="H596">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I596" s="2">
         <f t="shared" si="18"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J596" s="2">
         <f t="shared" si="19"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="L596">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M596">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="N596">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O596">
         <v>0</v>
@@ -44886,7 +44882,7 @@
         <v>0</v>
       </c>
       <c r="V596">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W596">
         <v>0</v>
@@ -44915,24 +44911,24 @@
         <v>62</v>
       </c>
       <c r="H597">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I597" s="2">
         <f t="shared" si="18"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J597" s="2">
         <f t="shared" ref="J597:J598" si="20">H597*1.75</f>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
       <c r="L597">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M597">
-        <v>6.33</v>
+        <v>6.21</v>
       </c>
       <c r="N597">
-        <v>6.75</v>
+        <v>6.57</v>
       </c>
       <c r="O597">
         <v>1</v>
@@ -44985,15 +44981,15 @@
         <v>36</v>
       </c>
       <c r="H598">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I598" s="2">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J598" s="2">
         <f t="shared" si="20"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="K598" t="s">
         <v>156</v>
@@ -45131,15 +45127,15 @@
         <v>33</v>
       </c>
       <c r="H600">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I600" s="2">
         <f t="shared" si="21"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J600" s="2">
         <f t="shared" si="22"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="L600">
         <v>2</v>
@@ -45212,13 +45208,13 @@
         <v>3.5</v>
       </c>
       <c r="L601">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M601">
         <v>5.5</v>
       </c>
       <c r="N601">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="O601">
         <v>0</v>
@@ -45352,37 +45348,37 @@
         <v>1.75</v>
       </c>
       <c r="L603">
+        <v>3</v>
+      </c>
+      <c r="M603">
+        <v>5</v>
+      </c>
+      <c r="N603">
+        <v>4.67</v>
+      </c>
+      <c r="O603">
+        <v>0</v>
+      </c>
+      <c r="P603">
+        <v>0</v>
+      </c>
+      <c r="Q603">
+        <v>0</v>
+      </c>
+      <c r="R603">
+        <v>0</v>
+      </c>
+      <c r="S603">
+        <v>0</v>
+      </c>
+      <c r="T603">
+        <v>0</v>
+      </c>
+      <c r="U603">
+        <v>0</v>
+      </c>
+      <c r="V603">
         <v>2</v>
-      </c>
-      <c r="M603">
-        <v>4.75</v>
-      </c>
-      <c r="N603">
-        <v>4.5</v>
-      </c>
-      <c r="O603">
-        <v>0</v>
-      </c>
-      <c r="P603">
-        <v>0</v>
-      </c>
-      <c r="Q603">
-        <v>0</v>
-      </c>
-      <c r="R603">
-        <v>0</v>
-      </c>
-      <c r="S603">
-        <v>0</v>
-      </c>
-      <c r="T603">
-        <v>0</v>
-      </c>
-      <c r="U603">
-        <v>0</v>
-      </c>
-      <c r="V603">
-        <v>1</v>
       </c>
       <c r="W603">
         <v>0</v>
@@ -45422,13 +45418,13 @@
         <v>3.5</v>
       </c>
       <c r="L604">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M604">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="N604">
-        <v>5.7</v>
+        <v>5.58</v>
       </c>
       <c r="O604">
         <v>0</v>
